--- a/javitolap.xlsx
+++ b/javitolap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Peter\Desktop\2026_alapvizsga\2026_alapvizsga_eles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0247B0A5-58D2-4BC5-8E9B-C7397E9B7B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D160FC8-90C9-4FE9-B460-0CFEE5E9B1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Webprogramozas" sheetId="5" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Alapbeállítások elvégzése</t>
   </si>
   <si>
-    <t>VENDEG_NET hálózat beállítása </t>
-  </si>
-  <si>
     <t>Magyar nyelv beállítása</t>
   </si>
   <si>
@@ -183,12 +180,262 @@
     <t>helyesen használta a with open()-t</t>
   </si>
   <si>
+    <t>A forgalomirányítókon a csatlakoztatott interfészek felkapcsolt állapotban vannak.</t>
+  </si>
+  <si>
+    <t>Minden hálózati eszköznek (a forgalomirányítóknak és a kapcsolóknak) a megadott nevet beállította.</t>
+  </si>
+  <si>
+    <t>Bera Sára Laura</t>
+  </si>
+  <si>
+    <t>Bihari Zsolt</t>
+  </si>
+  <si>
+    <t>Botlik Csongor</t>
+  </si>
+  <si>
+    <t>Bozóki Benedek Varsány</t>
+  </si>
+  <si>
+    <t>Búza Leonárd</t>
+  </si>
+  <si>
+    <t>Dunai Sándor Erik</t>
+  </si>
+  <si>
+    <t>Faragó Levente Balázs</t>
+  </si>
+  <si>
+    <t>Halmi Ádám István</t>
+  </si>
+  <si>
+    <t>Koczán Balázs</t>
+  </si>
+  <si>
+    <t>Magyar Hanna</t>
+  </si>
+  <si>
+    <t>Ordas Bence</t>
+  </si>
+  <si>
+    <t>Martinek Viktor</t>
+  </si>
+  <si>
+    <t>Papdi Milán</t>
+  </si>
+  <si>
+    <t>Papp Bence</t>
+  </si>
+  <si>
+    <t>Sőreg János Gábor</t>
+  </si>
+  <si>
+    <t>Tajti Máté</t>
+  </si>
+  <si>
+    <t>Tóth Levente</t>
+  </si>
+  <si>
+    <t>Bootstrap css állomány beimportálása</t>
+  </si>
+  <si>
+    <t>5.</t>
+  </si>
+  <si>
+    <t>6.</t>
+  </si>
+  <si>
+    <t>7.</t>
+  </si>
+  <si>
+    <t>8.</t>
+  </si>
+  <si>
+    <t>9.</t>
+  </si>
+  <si>
+    <t>10.</t>
+  </si>
+  <si>
+    <t>11.</t>
+  </si>
+  <si>
+    <t>12.</t>
+  </si>
+  <si>
+    <t>13.</t>
+  </si>
+  <si>
+    <t>14.</t>
+  </si>
+  <si>
+    <t>15.</t>
+  </si>
+  <si>
+    <t>16.</t>
+  </si>
+  <si>
+    <t>17.</t>
+  </si>
+  <si>
+    <t>Az oldal reszponzív</t>
+  </si>
+  <si>
+    <t>Az oldal háttérszíne #F6F3EF</t>
+  </si>
+  <si>
+    <t>jumbotron id-vel elem létrehozása</t>
+  </si>
+  <si>
+    <t>45em magasság beállítása</t>
+  </si>
+  <si>
+    <t>background-size helyes beállítása</t>
+  </si>
+  <si>
+    <t>nav háttérszíne #AFD695</t>
+  </si>
+  <si>
+    <t>Blog középre zárt</t>
+  </si>
+  <si>
+    <t>Blog display-1</t>
+  </si>
+  <si>
+    <t>Blog m-4</t>
+  </si>
+  <si>
+    <t>Blog kép img-fluid</t>
+  </si>
+  <si>
+    <t>Blog kép w-100</t>
+  </si>
+  <si>
+    <t>container col-sm-4</t>
+  </si>
+  <si>
+    <t>termekeink.html beállítása</t>
+  </si>
+  <si>
+    <t>about.html beállítása</t>
+  </si>
+  <si>
+    <t>képek alatti szöveg h5</t>
+  </si>
+  <si>
+    <t>táblázat - rowspan használata</t>
+  </si>
+  <si>
+    <t>táblázat - border helyes beállítása</t>
+  </si>
+  <si>
+    <t>táblázat - első cellák félkövérek</t>
+  </si>
+  <si>
+    <t>lista - ul választása</t>
+  </si>
+  <si>
+    <t>lista - list-style-type</t>
+  </si>
+  <si>
+    <t>ins használata</t>
+  </si>
+  <si>
+    <t>b vagy strong használata</t>
+  </si>
+  <si>
+    <t>mark használata</t>
+  </si>
+  <si>
+    <t>media használata</t>
+  </si>
+  <si>
+    <t>nav #linkek { gap: 0.1px; }</t>
+  </si>
+  <si>
+    <t>lista - square</t>
+  </si>
+  <si>
+    <t>small használata</t>
+  </si>
+  <si>
+    <t>képek alatti szöveg text-align és p-3</t>
+  </si>
+  <si>
+    <t>2 pont</t>
+  </si>
+  <si>
+    <t>1 pont</t>
+  </si>
+  <si>
+    <t>for ciklus torták feltöltéséhez</t>
+  </si>
+  <si>
+    <t>sorok strip().split(";")</t>
+  </si>
+  <si>
+    <t>Torták számát meghatározta</t>
+  </si>
+  <si>
+    <t>Kiíratás helyesen</t>
+  </si>
+  <si>
+    <t>for ciklus használata</t>
+  </si>
+  <si>
+    <t>return érték</t>
+  </si>
+  <si>
+    <t>függvény helyes hívása</t>
+  </si>
+  <si>
+    <t>f.write()</t>
+  </si>
+  <si>
+    <t>rendeles metódus helyes létrehozása</t>
+  </si>
+  <si>
+    <t>random beimportálása</t>
+  </si>
+  <si>
+    <t>osszrendeles függvény</t>
+  </si>
+  <si>
+    <t>Lista létrehozása</t>
+  </si>
+  <si>
+    <t>Függvényhívás helyesen</t>
+  </si>
+  <si>
+    <t>minErtek és maxErtek bekérése</t>
+  </si>
+  <si>
+    <t>cakes listát létrehozta</t>
+  </si>
+  <si>
+    <t>cakes feltöltése</t>
+  </si>
+  <si>
+    <t>huszonnegyLaktozmentesOsszege-t helyesen létrehozta</t>
+  </si>
+  <si>
+    <t>Cake osztály helyes létrehozása</t>
+  </si>
+  <si>
+    <t>olcsoLaktozmentesSzamlalas metódus helyes létrehozása</t>
+  </si>
+  <si>
+    <t>Cake helyes létrehozás</t>
+  </si>
+  <si>
+    <t>cakes lista létrehozása és feltoltese</t>
+  </si>
+  <si>
+    <t>Cakes keverése</t>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
       <t xml:space="preserve">A kész feladat legalább 6 eszközt tartalmaz, és a hálózatot </t>
     </r>
     <r>
@@ -197,8 +444,10 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
       </rPr>
-      <t>termeles2025/gyartas2025</t>
+      <t>zooszeged2026</t>
     </r>
     <r>
       <rPr>
@@ -210,46 +459,35 @@
     </r>
   </si>
   <si>
-    <t>A GYAR_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
-  </si>
-  <si>
-    <t>Az IRODA_RT/ TELEPHELY_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
-  </si>
-  <si>
-    <t>Az UZLET_RT/BEMUTATOTEREM_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
-  </si>
-  <si>
-    <t>A GYAR_SW kapcsoló felügyeleti interfészén az IP-címet és az alhálózati maszkot jól beállította. 172.30.0.2        255.255.0.0</t>
-  </si>
-  <si>
-    <t>A GYAR_SW kapcsolón az alapértelmezett átjáró IP-címét jól beállította.         172.30.0.1</t>
-  </si>
-  <si>
-    <t>A 3PC és a SZERVER számára helyes IP‑címet és alhálózati maszkot állított be.</t>
-  </si>
-  <si>
-    <t>A 3PC és a SZERVER számára helyes alapértelmezett átjárót állított be.</t>
-  </si>
-  <si>
-    <t>A 3PC és a SZERVER számára helyes DNS kiszolgáló címet állított be. 13.13.13.13</t>
-  </si>
-  <si>
-    <t>A UGYFEL_WIFI eszköz internet portján megfelelő IP-címet, alhálózati maszkot, alapértelmezett átjárót és DNS kiszolgáló címet állított be. 172.30.0.3  255.255.0.0.   172.30.0.1  13.13.13.13</t>
-  </si>
-  <si>
-    <t>A forgalomirányítókon a csatlakoztatott interfészek felkapcsolt állapotban vannak.</t>
-  </si>
-  <si>
-    <t>Minden hálózati eszköznek (a forgalomirányítóknak és a kapcsolóknak) a megadott nevet beállította.</t>
+    <t>Az IRODA_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
+  </si>
+  <si>
+    <t>A SHOP_SW kapcsoló felügyeleti interfészén az IP-címet és az alhálózati maszkot jól beállította. 172.30.0.2        255.255.0.0</t>
+  </si>
+  <si>
+    <t>A SHOP_SW kapcsolón az alapértelmezett átjáró IP-címét jól beállította.         172.30.0.1</t>
+  </si>
+  <si>
+    <t>A 4 PC és a SZERVER számára helyes IP‑címet és alhálózati maszkot állított be.</t>
+  </si>
+  <si>
+    <t>A 4 PC és a SZERVER számára helyes alapértelmezett átjárót állított be.</t>
+  </si>
+  <si>
+    <t>A 4 PC és a SZERVER számára helyes DNS kiszolgáló címet állított be. 13.13.13.13</t>
+  </si>
+  <si>
+    <t>Az IGAZGATO_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
+  </si>
+  <si>
+    <t>Az ORVOS_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
+  </si>
+  <si>
+    <t>A SHOP_WIFI eszköz internet portján megfelelő IP-címet, alhálózati maszkot, alapértelmezett átjárót és DNS kiszolgáló címet állított be. 172.30.0.3  255.255.0.0.   172.30.0.1  13.13.13.13</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Az IRODA_SW/TELEPHELY_SW kapcsoló privilegizált jelszava a </t>
+      <t xml:space="preserve">Az IGAZGATO_SW kapcsoló privilegizált jelszava a </t>
     </r>
     <r>
       <rPr>
@@ -258,7 +496,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>enairoda/enatelep</t>
+      <t>enaigazgato</t>
     </r>
     <r>
       <rPr>
@@ -271,12 +509,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Az IRODA_SW/TELEPHELY_SW kapcsoló a konzol porthoz tartozó jelszavát és annak aktiválását az  megadta </t>
+      <t xml:space="preserve">Az IGAZGATO_SW kapcsoló a konzol porthoz tartozó jelszavát és annak aktiválását az  megadta </t>
     </r>
     <r>
       <rPr>
@@ -285,7 +518,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">coniroda/contelep </t>
+      <t xml:space="preserve">conigazgato </t>
     </r>
     <r>
       <rPr>
@@ -298,12 +531,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">Az IRODA_SW/TELEPHELY_SW kapcsoló a távoli eléréshez tartozó jelszavát és annak aktiválását a </t>
+      <t xml:space="preserve">Az IGAZGATO_SW kapcsoló a távoli eléréshez tartozó jelszavát és annak aktiválását a </t>
     </r>
     <r>
       <rPr>
@@ -312,7 +540,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>vtyiroda/vtytelep</t>
+      <t>vtyigazgato</t>
     </r>
     <r>
       <rPr>
@@ -324,15 +552,10 @@
     </r>
   </si>
   <si>
-    <t>A IRODA_SW/TELEPHELY_SW kapcsoló jelszavak nem olvashatók ki a futó konfiguráció megjelenítésekor.</t>
+    <t>A IGAZGATO_SW kapcsoló jelszavak nem olvashatók ki a futó konfiguráció megjelenítésekor.</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
       <t xml:space="preserve">Figyelmeztetést állított be </t>
     </r>
     <r>
@@ -342,19 +565,80 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>Tilos az illetektelen behatolas/belepes!</t>
+      <t>Tilos az allatok zavarasa!</t>
     </r>
   </si>
   <si>
-    <t>A VENDEG_WIFI eszköz LAN felőli IP-címét és alhálózati maszkját helyesen beállította. 192.168.100.1 255.255.255.0</t>
-  </si>
-  <si>
+    <t>UGYFEL_NET hálózat beállítása </t>
+  </si>
+  <si>
+    <t>A SHOP_WIFI eszköz LAN felőli IP-címét és alhálózati maszkját helyesen beállította. 192.168.100.1 255.255.255.0</t>
+  </si>
+  <si>
+    <r>
+      <t>Az SSID </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>VASARLO</t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
+      <t>-ra állította.</t>
+    </r>
+  </si>
+  <si>
+    <t>A forgalomirányítókon és az IGAZGATO_SW kapcsoló konfigurációját helyileg mentette. </t>
+  </si>
+  <si>
+    <r>
+      <t>WPA2 hitelesítést állított be, és a kulcs</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t> allatkert123</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>A DHCP szerverszolgáltatásnál a DNS szerver IP-címét helyesen beállította. (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>4.4.4.4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t>A DHCP szerver szolgáltatásnál a kezdő IP-címet és a maximális kliensszámot helyesen beállította. (</t>
     </r>
     <r>
@@ -364,7 +648,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t>5 és 200 / 10 és 120</t>
+      <t>20 és 60</t>
     </r>
     <r>
       <rPr>
@@ -375,331 +659,6 @@
       <t>)</t>
     </r>
   </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>A DHCP szerverszolgáltatásnál a DNS szerver IP-címét helyesen beállította. (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve"> 13.13.13.13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Az SSID </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>UGYEL/VASARLO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>-ra állította.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>WPA2 hitelesítést állított be, és a kulcs </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>termeles123/gyartas123</t>
-    </r>
-  </si>
-  <si>
-    <t>A forgalomirányítókon és az IRODA_SW/TELEPHELY_SW kapcsoló konfigurációját helyileg mentette. </t>
-  </si>
-  <si>
-    <t>Bera Sára Laura</t>
-  </si>
-  <si>
-    <t>Bihari Zsolt</t>
-  </si>
-  <si>
-    <t>Botlik Csongor</t>
-  </si>
-  <si>
-    <t>Bozóki Benedek Varsány</t>
-  </si>
-  <si>
-    <t>Búza Leonárd</t>
-  </si>
-  <si>
-    <t>Dunai Sándor Erik</t>
-  </si>
-  <si>
-    <t>Faragó Levente Balázs</t>
-  </si>
-  <si>
-    <t>Halmi Ádám István</t>
-  </si>
-  <si>
-    <t>Koczán Balázs</t>
-  </si>
-  <si>
-    <t>Magyar Hanna</t>
-  </si>
-  <si>
-    <t>Ordas Bence</t>
-  </si>
-  <si>
-    <t>Martinek Viktor</t>
-  </si>
-  <si>
-    <t>Papdi Milán</t>
-  </si>
-  <si>
-    <t>Papp Bence</t>
-  </si>
-  <si>
-    <t>Sőreg János Gábor</t>
-  </si>
-  <si>
-    <t>Tajti Máté</t>
-  </si>
-  <si>
-    <t>Tóth Levente</t>
-  </si>
-  <si>
-    <t>Bootstrap css állomány beimportálása</t>
-  </si>
-  <si>
-    <t>5.</t>
-  </si>
-  <si>
-    <t>6.</t>
-  </si>
-  <si>
-    <t>7.</t>
-  </si>
-  <si>
-    <t>8.</t>
-  </si>
-  <si>
-    <t>9.</t>
-  </si>
-  <si>
-    <t>10.</t>
-  </si>
-  <si>
-    <t>11.</t>
-  </si>
-  <si>
-    <t>12.</t>
-  </si>
-  <si>
-    <t>13.</t>
-  </si>
-  <si>
-    <t>14.</t>
-  </si>
-  <si>
-    <t>15.</t>
-  </si>
-  <si>
-    <t>16.</t>
-  </si>
-  <si>
-    <t>17.</t>
-  </si>
-  <si>
-    <t>Az oldal reszponzív</t>
-  </si>
-  <si>
-    <t>Az oldal háttérszíne #F6F3EF</t>
-  </si>
-  <si>
-    <t>jumbotron id-vel elem létrehozása</t>
-  </si>
-  <si>
-    <t>45em magasság beállítása</t>
-  </si>
-  <si>
-    <t>background-size helyes beállítása</t>
-  </si>
-  <si>
-    <t>nav háttérszíne #AFD695</t>
-  </si>
-  <si>
-    <t>Blog középre zárt</t>
-  </si>
-  <si>
-    <t>Blog display-1</t>
-  </si>
-  <si>
-    <t>Blog m-4</t>
-  </si>
-  <si>
-    <t>Blog kép img-fluid</t>
-  </si>
-  <si>
-    <t>Blog kép w-100</t>
-  </si>
-  <si>
-    <t>container col-sm-4</t>
-  </si>
-  <si>
-    <t>termekeink.html beállítása</t>
-  </si>
-  <si>
-    <t>about.html beállítása</t>
-  </si>
-  <si>
-    <t>képek alatti szöveg h5</t>
-  </si>
-  <si>
-    <t>táblázat - rowspan használata</t>
-  </si>
-  <si>
-    <t>táblázat - border helyes beállítása</t>
-  </si>
-  <si>
-    <t>táblázat - első cellák félkövérek</t>
-  </si>
-  <si>
-    <t>lista - ul választása</t>
-  </si>
-  <si>
-    <t>lista - list-style-type</t>
-  </si>
-  <si>
-    <t>ins használata</t>
-  </si>
-  <si>
-    <t>b vagy strong használata</t>
-  </si>
-  <si>
-    <t>mark használata</t>
-  </si>
-  <si>
-    <t>media használata</t>
-  </si>
-  <si>
-    <t>nav #linkek { gap: 0.1px; }</t>
-  </si>
-  <si>
-    <t>lista - square</t>
-  </si>
-  <si>
-    <t>small használata</t>
-  </si>
-  <si>
-    <t>képek alatti szöveg text-align és p-3</t>
-  </si>
-  <si>
-    <t>2 pont</t>
-  </si>
-  <si>
-    <t>1 pont</t>
-  </si>
-  <si>
-    <t>for ciklus torták feltöltéséhez</t>
-  </si>
-  <si>
-    <t>sorok strip().split(";")</t>
-  </si>
-  <si>
-    <t>Torták számát meghatározta</t>
-  </si>
-  <si>
-    <t>Kiíratás helyesen</t>
-  </si>
-  <si>
-    <t>for ciklus használata</t>
-  </si>
-  <si>
-    <t>return érték</t>
-  </si>
-  <si>
-    <t>függvény helyes hívása</t>
-  </si>
-  <si>
-    <t>f.write()</t>
-  </si>
-  <si>
-    <t>rendeles metódus helyes létrehozása</t>
-  </si>
-  <si>
-    <t>random beimportálása</t>
-  </si>
-  <si>
-    <t>osszrendeles függvény</t>
-  </si>
-  <si>
-    <t>Lista létrehozása</t>
-  </si>
-  <si>
-    <t>Függvényhívás helyesen</t>
-  </si>
-  <si>
-    <t>minErtek és maxErtek bekérése</t>
-  </si>
-  <si>
-    <t>cakes listát létrehozta</t>
-  </si>
-  <si>
-    <t>cakes feltöltése</t>
-  </si>
-  <si>
-    <t>huszonnegyLaktozmentesOsszege-t helyesen létrehozta</t>
-  </si>
-  <si>
-    <t>Cake osztály helyes létrehozása</t>
-  </si>
-  <si>
-    <t>olcsoLaktozmentesSzamlalas metódus helyes létrehozása</t>
-  </si>
-  <si>
-    <t>Cake helyes létrehozás</t>
-  </si>
-  <si>
-    <t>cakes lista létrehozása és feltoltese</t>
-  </si>
-  <si>
-    <t>Cakes keverése</t>
-  </si>
 </sst>
 </file>
 
@@ -709,7 +668,7 @@
     <numFmt numFmtId="164" formatCode="0&quot; pont&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot; pont&quot;"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,6 +805,14 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
     </font>
   </fonts>
   <fills count="24">
@@ -1156,7 +1123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment textRotation="90"/>
@@ -1292,9 +1259,6 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1323,9 +1287,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1351,6 +1312,24 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -1587,55 +1566,55 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -1644,7 +1623,7 @@
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="B2" s="43">
         <v>1</v>
@@ -1703,7 +1682,7 @@
     </row>
     <row r="3" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="46">
         <v>1</v>
@@ -1762,7 +1741,7 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="48" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="49">
         <v>1</v>
@@ -1821,7 +1800,7 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="49">
         <v>1</v>
@@ -1880,7 +1859,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="49">
         <v>1</v>
@@ -1938,8 +1917,8 @@
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="81" t="s">
-        <v>97</v>
+      <c r="A7" s="79" t="s">
+        <v>75</v>
       </c>
       <c r="B7" s="49">
         <v>1</v>
@@ -1964,7 +1943,7 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="52">
         <v>1</v>
@@ -2023,7 +2002,7 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="52">
         <v>1</v>
@@ -2081,8 +2060,8 @@
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="81" t="s">
-        <v>98</v>
+      <c r="A10" s="79" t="s">
+        <v>76</v>
       </c>
       <c r="B10" s="49">
         <v>1</v>
@@ -2141,7 +2120,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="B11" s="52">
         <v>1</v>
@@ -2200,7 +2179,7 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="52">
         <v>1</v>
@@ -2258,8 +2237,8 @@
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="81" t="s">
-        <v>99</v>
+      <c r="A13" s="79" t="s">
+        <v>77</v>
       </c>
       <c r="B13" s="49">
         <v>1</v>
@@ -2317,8 +2296,8 @@
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="81" t="s">
-        <v>100</v>
+      <c r="A14" s="79" t="s">
+        <v>78</v>
       </c>
       <c r="B14" s="49">
         <v>1</v>
@@ -2377,7 +2356,7 @@
     </row>
     <row r="15" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="49">
         <v>1</v>
@@ -2435,8 +2414,8 @@
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="81" t="s">
-        <v>101</v>
+      <c r="A16" s="79" t="s">
+        <v>79</v>
       </c>
       <c r="B16" s="49">
         <v>1</v>
@@ -2495,7 +2474,7 @@
     </row>
     <row r="17" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B17" s="55">
         <v>1</v>
@@ -2554,7 +2533,7 @@
     </row>
     <row r="18" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B18" s="55">
         <v>1</v>
@@ -2613,7 +2592,7 @@
     </row>
     <row r="19" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="B19" s="55">
         <v>1</v>
@@ -2672,7 +2651,7 @@
     </row>
     <row r="20" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B20" s="55">
         <v>1</v>
@@ -2731,7 +2710,7 @@
     </row>
     <row r="21" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B21" s="55">
         <v>1</v>
@@ -2790,7 +2769,7 @@
     </row>
     <row r="22" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B22" s="55">
         <v>2</v>
@@ -2848,8 +2827,8 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="81" t="s">
-        <v>109</v>
+      <c r="A23" s="79" t="s">
+        <v>87</v>
       </c>
       <c r="B23" s="49">
         <v>1</v>
@@ -2907,8 +2886,8 @@
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="81" t="s">
-        <v>110</v>
+      <c r="A24" s="79" t="s">
+        <v>88</v>
       </c>
       <c r="B24" s="49">
         <v>1</v>
@@ -2967,7 +2946,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="53" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B25" s="52">
         <v>1</v>
@@ -3026,7 +3005,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B26" s="52">
         <v>1</v>
@@ -3085,7 +3064,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B27" s="52">
         <v>2</v>
@@ -3143,8 +3122,8 @@
       </c>
     </row>
     <row r="28" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="81" t="s">
-        <v>111</v>
+      <c r="A28" s="79" t="s">
+        <v>89</v>
       </c>
       <c r="B28" s="49">
         <v>1</v>
@@ -3202,8 +3181,8 @@
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="81" t="s">
-        <v>124</v>
+      <c r="A29" s="79" t="s">
+        <v>102</v>
       </c>
       <c r="B29" s="49">
         <v>1</v>
@@ -3262,7 +3241,7 @@
     </row>
     <row r="30" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B30" s="55">
         <v>1</v>
@@ -3321,7 +3300,7 @@
     </row>
     <row r="31" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B31" s="55">
         <v>1</v>
@@ -3380,7 +3359,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B32" s="52">
         <v>1</v>
@@ -3438,10 +3417,10 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="B33" s="79">
+      <c r="A33" s="79" t="s">
+        <v>95</v>
+      </c>
+      <c r="B33" s="77">
         <v>1</v>
       </c>
       <c r="C33" s="50">
@@ -3497,10 +3476,10 @@
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A34" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="B34" s="79">
+      <c r="A34" s="79" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" s="77">
         <v>1</v>
       </c>
       <c r="C34" s="50">
@@ -3556,10 +3535,10 @@
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A35" s="80" t="s">
-        <v>118</v>
-      </c>
-      <c r="B35" s="79">
+      <c r="A35" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="77">
         <v>1</v>
       </c>
       <c r="C35" s="50">
@@ -3615,8 +3594,8 @@
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A36" s="82" t="s">
-        <v>119</v>
+      <c r="A36" s="80" t="s">
+        <v>97</v>
       </c>
       <c r="B36" s="58">
         <v>1</v>
@@ -3675,7 +3654,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B37" s="56">
         <v>2</v>
@@ -3733,8 +3712,8 @@
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A38" s="83" t="s">
-        <v>121</v>
+      <c r="A38" s="81" t="s">
+        <v>99</v>
       </c>
       <c r="B38" s="43">
         <v>1</v>
@@ -3884,55 +3863,55 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -3941,10 +3920,10 @@
     </row>
     <row r="2" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="B2" s="85" t="s">
-        <v>125</v>
+        <v>118</v>
+      </c>
+      <c r="B2" s="83" t="s">
+        <v>103</v>
       </c>
       <c r="C2" s="12">
         <v>0</v>
@@ -4000,10 +3979,10 @@
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="85" t="s">
-        <v>125</v>
+        <v>38</v>
+      </c>
+      <c r="B3" s="83" t="s">
+        <v>103</v>
       </c>
       <c r="C3" s="12">
         <v>0</v>
@@ -4059,10 +4038,10 @@
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="85" t="s">
-        <v>125</v>
+        <v>40</v>
+      </c>
+      <c r="B4" s="83" t="s">
+        <v>103</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -4118,10 +4097,10 @@
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="85" t="s">
-        <v>125</v>
+        <v>39</v>
+      </c>
+      <c r="B5" s="83" t="s">
+        <v>103</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -4176,11 +4155,11 @@
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="s">
-        <v>141</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>126</v>
+      <c r="A6" s="82" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="84" t="s">
+        <v>104</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -4236,10 +4215,10 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="87" t="s">
-        <v>126</v>
+        <v>41</v>
+      </c>
+      <c r="B7" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -4294,11 +4273,11 @@
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="90" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="87" t="s">
-        <v>126</v>
+      <c r="A8" s="88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -4354,10 +4333,10 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="87" t="s">
-        <v>126</v>
+        <v>106</v>
+      </c>
+      <c r="B9" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C9" s="18">
         <v>0</v>
@@ -4413,10 +4392,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="87" t="s">
-        <v>125</v>
+        <v>120</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>103</v>
       </c>
       <c r="C10" s="18">
         <v>0</v>
@@ -4472,10 +4451,10 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B11" s="87" t="s">
-        <v>126</v>
+        <v>107</v>
+      </c>
+      <c r="B11" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C11" s="18">
         <v>0</v>
@@ -4531,10 +4510,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="B12" s="87" t="s">
-        <v>126</v>
+        <v>108</v>
+      </c>
+      <c r="B12" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C12" s="18">
         <v>0</v>
@@ -4590,10 +4569,10 @@
     </row>
     <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="B13" s="87" t="s">
-        <v>126</v>
+        <v>121</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -4649,10 +4628,10 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="B14" s="87" t="s">
-        <v>126</v>
+        <v>109</v>
+      </c>
+      <c r="B14" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -4708,10 +4687,10 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="87" t="s">
-        <v>126</v>
+        <v>110</v>
+      </c>
+      <c r="B15" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -4767,10 +4746,10 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="87" t="s">
-        <v>126</v>
+        <v>111</v>
+      </c>
+      <c r="B16" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -4826,10 +4805,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="87" t="s">
-        <v>126</v>
+        <v>41</v>
+      </c>
+      <c r="B17" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -4885,10 +4864,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="B18" s="87" t="s">
-        <v>126</v>
+        <v>112</v>
+      </c>
+      <c r="B18" s="85" t="s">
+        <v>104</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -4943,11 +4922,11 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="91" t="s">
-        <v>144</v>
-      </c>
-      <c r="B19" s="88" t="s">
-        <v>125</v>
+      <c r="A19" s="89" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C19" s="19">
         <v>0</v>
@@ -5003,10 +4982,10 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="88" t="s">
-        <v>125</v>
+        <v>14</v>
+      </c>
+      <c r="B20" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -5062,10 +5041,10 @@
     </row>
     <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="88" t="s">
-        <v>125</v>
+        <v>123</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -5121,10 +5100,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="88" t="s">
-        <v>125</v>
+        <v>113</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -5180,10 +5159,10 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="88" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="B23" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -5239,10 +5218,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B24" s="88" t="s">
-        <v>126</v>
+        <v>124</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C24" s="19">
         <v>0</v>
@@ -5298,10 +5277,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B25" s="88" t="s">
         <v>125</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>103</v>
       </c>
       <c r="C25" s="19">
         <v>0</v>
@@ -5357,10 +5336,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="B26" s="88" t="s">
-        <v>126</v>
+        <v>114</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C26" s="19">
         <v>0</v>
@@ -5416,10 +5395,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B27" s="88" t="s">
         <v>126</v>
+      </c>
+      <c r="B27" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
@@ -5475,10 +5454,10 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" s="88" t="s">
-        <v>126</v>
+        <v>115</v>
+      </c>
+      <c r="B28" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
@@ -5534,10 +5513,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="B29" s="88" t="s">
-        <v>126</v>
+        <v>116</v>
+      </c>
+      <c r="B29" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -5559,10 +5538,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="B30" s="88" t="s">
-        <v>126</v>
+        <v>117</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>104</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
@@ -5617,7 +5596,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B31" s="89">
+      <c r="B31" s="87">
         <v>40</v>
       </c>
       <c r="C31" s="2">
@@ -5712,55 +5691,55 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D1" s="41" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E1" s="41" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="F1" s="41" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="G1" s="41" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="H1" s="41" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="I1" s="41" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="J1" s="41" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="K1" s="41" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="M1" s="41" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="N1" s="41" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="P1" s="41" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="Q1" s="41" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="R1" s="41" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="S1" s="41" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
@@ -5791,8 +5770,8 @@
       <c r="S2" s="3"/>
     </row>
     <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
-        <v>43</v>
+      <c r="A3" s="90" t="s">
+        <v>127</v>
       </c>
       <c r="B3" s="61">
         <v>1</v>
@@ -6109,592 +6088,592 @@
       <c r="S8" s="3"/>
     </row>
     <row r="9" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="69">
+      <c r="A9" s="91" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="68">
         <v>3</v>
       </c>
-      <c r="C9" s="70">
-        <v>0</v>
-      </c>
-      <c r="D9" s="70">
-        <v>0</v>
-      </c>
-      <c r="E9" s="70">
-        <v>0</v>
-      </c>
-      <c r="F9" s="70">
-        <v>0</v>
-      </c>
-      <c r="G9" s="70">
-        <v>0</v>
-      </c>
-      <c r="H9" s="70">
-        <v>0</v>
-      </c>
-      <c r="I9" s="70">
-        <v>0</v>
-      </c>
-      <c r="J9" s="70">
-        <v>0</v>
-      </c>
-      <c r="K9" s="70">
-        <v>0</v>
-      </c>
-      <c r="L9" s="70">
-        <v>0</v>
-      </c>
-      <c r="M9" s="70">
-        <v>0</v>
-      </c>
-      <c r="N9" s="70">
-        <v>0</v>
-      </c>
-      <c r="O9" s="70">
-        <v>0</v>
-      </c>
-      <c r="P9" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="70">
-        <v>0</v>
-      </c>
-      <c r="R9" s="70">
-        <v>0</v>
-      </c>
-      <c r="S9" s="70">
+      <c r="C9" s="69">
+        <v>0</v>
+      </c>
+      <c r="D9" s="69">
+        <v>0</v>
+      </c>
+      <c r="E9" s="69">
+        <v>0</v>
+      </c>
+      <c r="F9" s="69">
+        <v>0</v>
+      </c>
+      <c r="G9" s="69">
+        <v>0</v>
+      </c>
+      <c r="H9" s="69">
+        <v>0</v>
+      </c>
+      <c r="I9" s="69">
+        <v>0</v>
+      </c>
+      <c r="J9" s="69">
+        <v>0</v>
+      </c>
+      <c r="K9" s="69">
+        <v>0</v>
+      </c>
+      <c r="L9" s="69">
+        <v>0</v>
+      </c>
+      <c r="M9" s="69">
+        <v>0</v>
+      </c>
+      <c r="N9" s="69">
+        <v>0</v>
+      </c>
+      <c r="O9" s="69">
+        <v>0</v>
+      </c>
+      <c r="P9" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="69">
+        <v>0</v>
+      </c>
+      <c r="R9" s="69">
+        <v>0</v>
+      </c>
+      <c r="S9" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="69">
+      <c r="A10" s="91" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="68">
         <v>2</v>
       </c>
-      <c r="C10" s="70">
-        <v>0</v>
-      </c>
-      <c r="D10" s="70">
-        <v>0</v>
-      </c>
-      <c r="E10" s="70">
-        <v>0</v>
-      </c>
-      <c r="F10" s="70">
-        <v>0</v>
-      </c>
-      <c r="G10" s="70">
-        <v>0</v>
-      </c>
-      <c r="H10" s="70">
-        <v>0</v>
-      </c>
-      <c r="I10" s="70">
-        <v>0</v>
-      </c>
-      <c r="J10" s="70">
-        <v>0</v>
-      </c>
-      <c r="K10" s="70">
-        <v>0</v>
-      </c>
-      <c r="L10" s="70">
-        <v>0</v>
-      </c>
-      <c r="M10" s="70">
-        <v>0</v>
-      </c>
-      <c r="N10" s="70">
-        <v>0</v>
-      </c>
-      <c r="O10" s="70">
-        <v>0</v>
-      </c>
-      <c r="P10" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="70">
-        <v>0</v>
-      </c>
-      <c r="R10" s="70">
-        <v>0</v>
-      </c>
-      <c r="S10" s="70">
+      <c r="C10" s="69">
+        <v>0</v>
+      </c>
+      <c r="D10" s="69">
+        <v>0</v>
+      </c>
+      <c r="E10" s="69">
+        <v>0</v>
+      </c>
+      <c r="F10" s="69">
+        <v>0</v>
+      </c>
+      <c r="G10" s="69">
+        <v>0</v>
+      </c>
+      <c r="H10" s="69">
+        <v>0</v>
+      </c>
+      <c r="I10" s="69">
+        <v>0</v>
+      </c>
+      <c r="J10" s="69">
+        <v>0</v>
+      </c>
+      <c r="K10" s="69">
+        <v>0</v>
+      </c>
+      <c r="L10" s="69">
+        <v>0</v>
+      </c>
+      <c r="M10" s="69">
+        <v>0</v>
+      </c>
+      <c r="N10" s="69">
+        <v>0</v>
+      </c>
+      <c r="O10" s="69">
+        <v>0</v>
+      </c>
+      <c r="P10" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="69">
+        <v>0</v>
+      </c>
+      <c r="R10" s="69">
+        <v>0</v>
+      </c>
+      <c r="S10" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="69">
+      <c r="A11" s="91" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="68">
         <v>2</v>
       </c>
-      <c r="C11" s="70">
-        <v>0</v>
-      </c>
-      <c r="D11" s="70">
-        <v>0</v>
-      </c>
-      <c r="E11" s="70">
-        <v>0</v>
-      </c>
-      <c r="F11" s="70">
-        <v>0</v>
-      </c>
-      <c r="G11" s="70">
-        <v>0</v>
-      </c>
-      <c r="H11" s="70">
-        <v>0</v>
-      </c>
-      <c r="I11" s="70">
-        <v>0</v>
-      </c>
-      <c r="J11" s="70">
-        <v>0</v>
-      </c>
-      <c r="K11" s="70">
-        <v>0</v>
-      </c>
-      <c r="L11" s="70">
-        <v>0</v>
-      </c>
-      <c r="M11" s="70">
-        <v>0</v>
-      </c>
-      <c r="N11" s="70">
-        <v>0</v>
-      </c>
-      <c r="O11" s="70">
-        <v>0</v>
-      </c>
-      <c r="P11" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="70">
-        <v>0</v>
-      </c>
-      <c r="R11" s="70">
-        <v>0</v>
-      </c>
-      <c r="S11" s="70">
+      <c r="C11" s="69">
+        <v>0</v>
+      </c>
+      <c r="D11" s="69">
+        <v>0</v>
+      </c>
+      <c r="E11" s="69">
+        <v>0</v>
+      </c>
+      <c r="F11" s="69">
+        <v>0</v>
+      </c>
+      <c r="G11" s="69">
+        <v>0</v>
+      </c>
+      <c r="H11" s="69">
+        <v>0</v>
+      </c>
+      <c r="I11" s="69">
+        <v>0</v>
+      </c>
+      <c r="J11" s="69">
+        <v>0</v>
+      </c>
+      <c r="K11" s="69">
+        <v>0</v>
+      </c>
+      <c r="L11" s="69">
+        <v>0</v>
+      </c>
+      <c r="M11" s="69">
+        <v>0</v>
+      </c>
+      <c r="N11" s="69">
+        <v>0</v>
+      </c>
+      <c r="O11" s="69">
+        <v>0</v>
+      </c>
+      <c r="P11" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="69">
+        <v>0</v>
+      </c>
+      <c r="R11" s="69">
+        <v>0</v>
+      </c>
+      <c r="S11" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="69">
+      <c r="A12" s="91" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="68">
         <v>1</v>
       </c>
-      <c r="C12" s="70">
-        <v>0</v>
-      </c>
-      <c r="D12" s="70">
-        <v>0</v>
-      </c>
-      <c r="E12" s="70">
-        <v>0</v>
-      </c>
-      <c r="F12" s="70">
-        <v>0</v>
-      </c>
-      <c r="G12" s="70">
-        <v>0</v>
-      </c>
-      <c r="H12" s="70">
-        <v>0</v>
-      </c>
-      <c r="I12" s="70">
-        <v>0</v>
-      </c>
-      <c r="J12" s="70">
-        <v>0</v>
-      </c>
-      <c r="K12" s="70">
-        <v>0</v>
-      </c>
-      <c r="L12" s="70">
-        <v>0</v>
-      </c>
-      <c r="M12" s="70">
-        <v>0</v>
-      </c>
-      <c r="N12" s="70">
-        <v>0</v>
-      </c>
-      <c r="O12" s="70">
-        <v>0</v>
-      </c>
-      <c r="P12" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="70">
-        <v>0</v>
-      </c>
-      <c r="R12" s="70">
-        <v>0</v>
-      </c>
-      <c r="S12" s="70">
+      <c r="C12" s="69">
+        <v>0</v>
+      </c>
+      <c r="D12" s="69">
+        <v>0</v>
+      </c>
+      <c r="E12" s="69">
+        <v>0</v>
+      </c>
+      <c r="F12" s="69">
+        <v>0</v>
+      </c>
+      <c r="G12" s="69">
+        <v>0</v>
+      </c>
+      <c r="H12" s="69">
+        <v>0</v>
+      </c>
+      <c r="I12" s="69">
+        <v>0</v>
+      </c>
+      <c r="J12" s="69">
+        <v>0</v>
+      </c>
+      <c r="K12" s="69">
+        <v>0</v>
+      </c>
+      <c r="L12" s="69">
+        <v>0</v>
+      </c>
+      <c r="M12" s="69">
+        <v>0</v>
+      </c>
+      <c r="N12" s="69">
+        <v>0</v>
+      </c>
+      <c r="O12" s="69">
+        <v>0</v>
+      </c>
+      <c r="P12" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="69">
+        <v>0</v>
+      </c>
+      <c r="R12" s="69">
+        <v>0</v>
+      </c>
+      <c r="S12" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="63" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="69">
+      <c r="A13" s="91" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="68">
         <v>1</v>
       </c>
-      <c r="C13" s="70">
-        <v>0</v>
-      </c>
-      <c r="D13" s="70">
-        <v>0</v>
-      </c>
-      <c r="E13" s="70">
-        <v>0</v>
-      </c>
-      <c r="F13" s="70">
-        <v>0</v>
-      </c>
-      <c r="G13" s="70">
-        <v>0</v>
-      </c>
-      <c r="H13" s="70">
-        <v>0</v>
-      </c>
-      <c r="I13" s="70">
-        <v>0</v>
-      </c>
-      <c r="J13" s="70">
-        <v>0</v>
-      </c>
-      <c r="K13" s="70">
-        <v>0</v>
-      </c>
-      <c r="L13" s="70">
-        <v>0</v>
-      </c>
-      <c r="M13" s="70">
-        <v>0</v>
-      </c>
-      <c r="N13" s="70">
-        <v>0</v>
-      </c>
-      <c r="O13" s="70">
-        <v>0</v>
-      </c>
-      <c r="P13" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="70">
-        <v>0</v>
-      </c>
-      <c r="R13" s="70">
-        <v>0</v>
-      </c>
-      <c r="S13" s="70">
+      <c r="C13" s="69">
+        <v>0</v>
+      </c>
+      <c r="D13" s="69">
+        <v>0</v>
+      </c>
+      <c r="E13" s="69">
+        <v>0</v>
+      </c>
+      <c r="F13" s="69">
+        <v>0</v>
+      </c>
+      <c r="G13" s="69">
+        <v>0</v>
+      </c>
+      <c r="H13" s="69">
+        <v>0</v>
+      </c>
+      <c r="I13" s="69">
+        <v>0</v>
+      </c>
+      <c r="J13" s="69">
+        <v>0</v>
+      </c>
+      <c r="K13" s="69">
+        <v>0</v>
+      </c>
+      <c r="L13" s="69">
+        <v>0</v>
+      </c>
+      <c r="M13" s="69">
+        <v>0</v>
+      </c>
+      <c r="N13" s="69">
+        <v>0</v>
+      </c>
+      <c r="O13" s="69">
+        <v>0</v>
+      </c>
+      <c r="P13" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="69">
+        <v>0</v>
+      </c>
+      <c r="R13" s="69">
+        <v>0</v>
+      </c>
+      <c r="S13" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="63" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="69">
+      <c r="A14" s="91" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="68">
         <v>4</v>
       </c>
-      <c r="C14" s="70">
-        <v>0</v>
-      </c>
-      <c r="D14" s="70">
-        <v>0</v>
-      </c>
-      <c r="E14" s="70">
-        <v>0</v>
-      </c>
-      <c r="F14" s="70">
-        <v>0</v>
-      </c>
-      <c r="G14" s="70">
-        <v>0</v>
-      </c>
-      <c r="H14" s="70">
-        <v>0</v>
-      </c>
-      <c r="I14" s="70">
-        <v>0</v>
-      </c>
-      <c r="J14" s="70">
-        <v>0</v>
-      </c>
-      <c r="K14" s="70">
-        <v>0</v>
-      </c>
-      <c r="L14" s="70">
-        <v>0</v>
-      </c>
-      <c r="M14" s="70">
-        <v>0</v>
-      </c>
-      <c r="N14" s="70">
-        <v>0</v>
-      </c>
-      <c r="O14" s="70">
-        <v>0</v>
-      </c>
-      <c r="P14" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="70">
-        <v>0</v>
-      </c>
-      <c r="R14" s="70">
-        <v>0</v>
-      </c>
-      <c r="S14" s="70">
+      <c r="C14" s="69">
+        <v>0</v>
+      </c>
+      <c r="D14" s="69">
+        <v>0</v>
+      </c>
+      <c r="E14" s="69">
+        <v>0</v>
+      </c>
+      <c r="F14" s="69">
+        <v>0</v>
+      </c>
+      <c r="G14" s="69">
+        <v>0</v>
+      </c>
+      <c r="H14" s="69">
+        <v>0</v>
+      </c>
+      <c r="I14" s="69">
+        <v>0</v>
+      </c>
+      <c r="J14" s="69">
+        <v>0</v>
+      </c>
+      <c r="K14" s="69">
+        <v>0</v>
+      </c>
+      <c r="L14" s="69">
+        <v>0</v>
+      </c>
+      <c r="M14" s="69">
+        <v>0</v>
+      </c>
+      <c r="N14" s="69">
+        <v>0</v>
+      </c>
+      <c r="O14" s="69">
+        <v>0</v>
+      </c>
+      <c r="P14" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="69">
+        <v>0</v>
+      </c>
+      <c r="R14" s="69">
+        <v>0</v>
+      </c>
+      <c r="S14" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="69">
+      <c r="A15" s="91" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="68">
         <v>1</v>
       </c>
-      <c r="C15" s="70">
-        <v>0</v>
-      </c>
-      <c r="D15" s="70">
-        <v>0</v>
-      </c>
-      <c r="E15" s="70">
-        <v>0</v>
-      </c>
-      <c r="F15" s="70">
-        <v>0</v>
-      </c>
-      <c r="G15" s="70">
-        <v>0</v>
-      </c>
-      <c r="H15" s="70">
-        <v>0</v>
-      </c>
-      <c r="I15" s="70">
-        <v>0</v>
-      </c>
-      <c r="J15" s="70">
-        <v>0</v>
-      </c>
-      <c r="K15" s="70">
-        <v>0</v>
-      </c>
-      <c r="L15" s="70">
-        <v>0</v>
-      </c>
-      <c r="M15" s="70">
-        <v>0</v>
-      </c>
-      <c r="N15" s="70">
-        <v>0</v>
-      </c>
-      <c r="O15" s="70">
-        <v>0</v>
-      </c>
-      <c r="P15" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="70">
-        <v>0</v>
-      </c>
-      <c r="R15" s="70">
-        <v>0</v>
-      </c>
-      <c r="S15" s="70">
+      <c r="C15" s="69">
+        <v>0</v>
+      </c>
+      <c r="D15" s="69">
+        <v>0</v>
+      </c>
+      <c r="E15" s="69">
+        <v>0</v>
+      </c>
+      <c r="F15" s="69">
+        <v>0</v>
+      </c>
+      <c r="G15" s="69">
+        <v>0</v>
+      </c>
+      <c r="H15" s="69">
+        <v>0</v>
+      </c>
+      <c r="I15" s="69">
+        <v>0</v>
+      </c>
+      <c r="J15" s="69">
+        <v>0</v>
+      </c>
+      <c r="K15" s="69">
+        <v>0</v>
+      </c>
+      <c r="L15" s="69">
+        <v>0</v>
+      </c>
+      <c r="M15" s="69">
+        <v>0</v>
+      </c>
+      <c r="N15" s="69">
+        <v>0</v>
+      </c>
+      <c r="O15" s="69">
+        <v>0</v>
+      </c>
+      <c r="P15" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="69">
+        <v>0</v>
+      </c>
+      <c r="R15" s="69">
+        <v>0</v>
+      </c>
+      <c r="S15" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="63" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="69">
+      <c r="A16" s="91" t="s">
+        <v>133</v>
+      </c>
+      <c r="B16" s="68">
         <v>1</v>
       </c>
-      <c r="C16" s="70">
-        <v>0</v>
-      </c>
-      <c r="D16" s="70">
-        <v>0</v>
-      </c>
-      <c r="E16" s="70">
-        <v>0</v>
-      </c>
-      <c r="F16" s="70">
-        <v>0</v>
-      </c>
-      <c r="G16" s="70">
-        <v>0</v>
-      </c>
-      <c r="H16" s="70">
-        <v>0</v>
-      </c>
-      <c r="I16" s="70">
-        <v>0</v>
-      </c>
-      <c r="J16" s="70">
-        <v>0</v>
-      </c>
-      <c r="K16" s="70">
-        <v>0</v>
-      </c>
-      <c r="L16" s="70">
-        <v>0</v>
-      </c>
-      <c r="M16" s="70">
-        <v>0</v>
-      </c>
-      <c r="N16" s="70">
-        <v>0</v>
-      </c>
-      <c r="O16" s="70">
-        <v>0</v>
-      </c>
-      <c r="P16" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="70">
-        <v>0</v>
-      </c>
-      <c r="R16" s="70">
-        <v>0</v>
-      </c>
-      <c r="S16" s="70">
+      <c r="C16" s="69">
+        <v>0</v>
+      </c>
+      <c r="D16" s="69">
+        <v>0</v>
+      </c>
+      <c r="E16" s="69">
+        <v>0</v>
+      </c>
+      <c r="F16" s="69">
+        <v>0</v>
+      </c>
+      <c r="G16" s="69">
+        <v>0</v>
+      </c>
+      <c r="H16" s="69">
+        <v>0</v>
+      </c>
+      <c r="I16" s="69">
+        <v>0</v>
+      </c>
+      <c r="J16" s="69">
+        <v>0</v>
+      </c>
+      <c r="K16" s="69">
+        <v>0</v>
+      </c>
+      <c r="L16" s="69">
+        <v>0</v>
+      </c>
+      <c r="M16" s="69">
+        <v>0</v>
+      </c>
+      <c r="N16" s="69">
+        <v>0</v>
+      </c>
+      <c r="O16" s="69">
+        <v>0</v>
+      </c>
+      <c r="P16" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="69">
+        <v>0</v>
+      </c>
+      <c r="R16" s="69">
+        <v>0</v>
+      </c>
+      <c r="S16" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="69">
+      <c r="A17" s="91" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="68">
         <v>4</v>
       </c>
-      <c r="C17" s="70">
-        <v>0</v>
-      </c>
-      <c r="D17" s="70">
-        <v>0</v>
-      </c>
-      <c r="E17" s="70">
-        <v>0</v>
-      </c>
-      <c r="F17" s="70">
-        <v>0</v>
-      </c>
-      <c r="G17" s="70">
-        <v>0</v>
-      </c>
-      <c r="H17" s="70">
-        <v>0</v>
-      </c>
-      <c r="I17" s="70">
-        <v>0</v>
-      </c>
-      <c r="J17" s="70">
-        <v>0</v>
-      </c>
-      <c r="K17" s="70">
-        <v>0</v>
-      </c>
-      <c r="L17" s="70">
-        <v>0</v>
-      </c>
-      <c r="M17" s="70">
-        <v>0</v>
-      </c>
-      <c r="N17" s="70">
-        <v>0</v>
-      </c>
-      <c r="O17" s="70">
-        <v>0</v>
-      </c>
-      <c r="P17" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="70">
-        <v>0</v>
-      </c>
-      <c r="R17" s="70">
-        <v>0</v>
-      </c>
-      <c r="S17" s="70">
+      <c r="C17" s="69">
+        <v>0</v>
+      </c>
+      <c r="D17" s="69">
+        <v>0</v>
+      </c>
+      <c r="E17" s="69">
+        <v>0</v>
+      </c>
+      <c r="F17" s="69">
+        <v>0</v>
+      </c>
+      <c r="G17" s="69">
+        <v>0</v>
+      </c>
+      <c r="H17" s="69">
+        <v>0</v>
+      </c>
+      <c r="I17" s="69">
+        <v>0</v>
+      </c>
+      <c r="J17" s="69">
+        <v>0</v>
+      </c>
+      <c r="K17" s="69">
+        <v>0</v>
+      </c>
+      <c r="L17" s="69">
+        <v>0</v>
+      </c>
+      <c r="M17" s="69">
+        <v>0</v>
+      </c>
+      <c r="N17" s="69">
+        <v>0</v>
+      </c>
+      <c r="O17" s="69">
+        <v>0</v>
+      </c>
+      <c r="P17" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="69">
+        <v>0</v>
+      </c>
+      <c r="R17" s="69">
+        <v>0</v>
+      </c>
+      <c r="S17" s="69">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="69">
+        <v>42</v>
+      </c>
+      <c r="B18" s="68">
         <v>1</v>
       </c>
-      <c r="C18" s="70">
-        <v>0</v>
-      </c>
-      <c r="D18" s="70">
-        <v>0</v>
-      </c>
-      <c r="E18" s="70">
-        <v>0</v>
-      </c>
-      <c r="F18" s="70">
-        <v>0</v>
-      </c>
-      <c r="G18" s="70">
-        <v>0</v>
-      </c>
-      <c r="H18" s="70">
-        <v>0</v>
-      </c>
-      <c r="I18" s="70">
-        <v>0</v>
-      </c>
-      <c r="J18" s="70">
-        <v>0</v>
-      </c>
-      <c r="K18" s="70">
-        <v>0</v>
-      </c>
-      <c r="L18" s="70">
-        <v>0</v>
-      </c>
-      <c r="M18" s="70">
-        <v>0</v>
-      </c>
-      <c r="N18" s="70">
-        <v>0</v>
-      </c>
-      <c r="O18" s="70">
-        <v>0</v>
-      </c>
-      <c r="P18" s="70">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="70">
-        <v>0</v>
-      </c>
-      <c r="R18" s="70">
-        <v>0</v>
-      </c>
-      <c r="S18" s="70">
+      <c r="C18" s="69">
+        <v>0</v>
+      </c>
+      <c r="D18" s="69">
+        <v>0</v>
+      </c>
+      <c r="E18" s="69">
+        <v>0</v>
+      </c>
+      <c r="F18" s="69">
+        <v>0</v>
+      </c>
+      <c r="G18" s="69">
+        <v>0</v>
+      </c>
+      <c r="H18" s="69">
+        <v>0</v>
+      </c>
+      <c r="I18" s="69">
+        <v>0</v>
+      </c>
+      <c r="J18" s="69">
+        <v>0</v>
+      </c>
+      <c r="K18" s="69">
+        <v>0</v>
+      </c>
+      <c r="L18" s="69">
+        <v>0</v>
+      </c>
+      <c r="M18" s="69">
+        <v>0</v>
+      </c>
+      <c r="N18" s="69">
+        <v>0</v>
+      </c>
+      <c r="O18" s="69">
+        <v>0</v>
+      </c>
+      <c r="P18" s="69">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="69">
+        <v>0</v>
+      </c>
+      <c r="R18" s="69">
+        <v>0</v>
+      </c>
+      <c r="S18" s="69">
         <v>0</v>
       </c>
     </row>
@@ -6723,361 +6702,361 @@
     </row>
     <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" s="71">
+        <v>43</v>
+      </c>
+      <c r="B20" s="70">
         <v>1</v>
       </c>
-      <c r="C20" s="72">
-        <v>0</v>
-      </c>
-      <c r="D20" s="72">
-        <v>0</v>
-      </c>
-      <c r="E20" s="72">
-        <v>0</v>
-      </c>
-      <c r="F20" s="72">
-        <v>0</v>
-      </c>
-      <c r="G20" s="72">
-        <v>0</v>
-      </c>
-      <c r="H20" s="72">
-        <v>0</v>
-      </c>
-      <c r="I20" s="72">
-        <v>0</v>
-      </c>
-      <c r="J20" s="72">
-        <v>0</v>
-      </c>
-      <c r="K20" s="72">
-        <v>0</v>
-      </c>
-      <c r="L20" s="72">
-        <v>0</v>
-      </c>
-      <c r="M20" s="72">
-        <v>0</v>
-      </c>
-      <c r="N20" s="72">
-        <v>0</v>
-      </c>
-      <c r="O20" s="72">
-        <v>0</v>
-      </c>
-      <c r="P20" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="72">
-        <v>0</v>
-      </c>
-      <c r="R20" s="72">
-        <v>0</v>
-      </c>
-      <c r="S20" s="72">
+      <c r="C20" s="71">
+        <v>0</v>
+      </c>
+      <c r="D20" s="71">
+        <v>0</v>
+      </c>
+      <c r="E20" s="71">
+        <v>0</v>
+      </c>
+      <c r="F20" s="71">
+        <v>0</v>
+      </c>
+      <c r="G20" s="71">
+        <v>0</v>
+      </c>
+      <c r="H20" s="71">
+        <v>0</v>
+      </c>
+      <c r="I20" s="71">
+        <v>0</v>
+      </c>
+      <c r="J20" s="71">
+        <v>0</v>
+      </c>
+      <c r="K20" s="71">
+        <v>0</v>
+      </c>
+      <c r="L20" s="71">
+        <v>0</v>
+      </c>
+      <c r="M20" s="71">
+        <v>0</v>
+      </c>
+      <c r="N20" s="71">
+        <v>0</v>
+      </c>
+      <c r="O20" s="71">
+        <v>0</v>
+      </c>
+      <c r="P20" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="71">
+        <v>0</v>
+      </c>
+      <c r="R20" s="71">
+        <v>0</v>
+      </c>
+      <c r="S20" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="71">
+      <c r="A21" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B21" s="70">
         <v>1</v>
       </c>
-      <c r="C21" s="72">
-        <v>0</v>
-      </c>
-      <c r="D21" s="72">
-        <v>0</v>
-      </c>
-      <c r="E21" s="72">
-        <v>0</v>
-      </c>
-      <c r="F21" s="72">
-        <v>0</v>
-      </c>
-      <c r="G21" s="72">
-        <v>0</v>
-      </c>
-      <c r="H21" s="72">
-        <v>0</v>
-      </c>
-      <c r="I21" s="72">
-        <v>0</v>
-      </c>
-      <c r="J21" s="72">
-        <v>0</v>
-      </c>
-      <c r="K21" s="72">
-        <v>0</v>
-      </c>
-      <c r="L21" s="72">
-        <v>0</v>
-      </c>
-      <c r="M21" s="72">
-        <v>0</v>
-      </c>
-      <c r="N21" s="72">
-        <v>0</v>
-      </c>
-      <c r="O21" s="72">
-        <v>0</v>
-      </c>
-      <c r="P21" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="72">
-        <v>0</v>
-      </c>
-      <c r="R21" s="72">
-        <v>0</v>
-      </c>
-      <c r="S21" s="72">
+      <c r="C21" s="71">
+        <v>0</v>
+      </c>
+      <c r="D21" s="71">
+        <v>0</v>
+      </c>
+      <c r="E21" s="71">
+        <v>0</v>
+      </c>
+      <c r="F21" s="71">
+        <v>0</v>
+      </c>
+      <c r="G21" s="71">
+        <v>0</v>
+      </c>
+      <c r="H21" s="71">
+        <v>0</v>
+      </c>
+      <c r="I21" s="71">
+        <v>0</v>
+      </c>
+      <c r="J21" s="71">
+        <v>0</v>
+      </c>
+      <c r="K21" s="71">
+        <v>0</v>
+      </c>
+      <c r="L21" s="71">
+        <v>0</v>
+      </c>
+      <c r="M21" s="71">
+        <v>0</v>
+      </c>
+      <c r="N21" s="71">
+        <v>0</v>
+      </c>
+      <c r="O21" s="71">
+        <v>0</v>
+      </c>
+      <c r="P21" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="71">
+        <v>0</v>
+      </c>
+      <c r="R21" s="71">
+        <v>0</v>
+      </c>
+      <c r="S21" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="71">
+      <c r="A22" s="93" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="70">
         <v>1</v>
       </c>
-      <c r="C22" s="72">
-        <v>0</v>
-      </c>
-      <c r="D22" s="72">
-        <v>0</v>
-      </c>
-      <c r="E22" s="72">
-        <v>0</v>
-      </c>
-      <c r="F22" s="72">
-        <v>0</v>
-      </c>
-      <c r="G22" s="72">
-        <v>0</v>
-      </c>
-      <c r="H22" s="72">
-        <v>0</v>
-      </c>
-      <c r="I22" s="72">
-        <v>0</v>
-      </c>
-      <c r="J22" s="72">
-        <v>0</v>
-      </c>
-      <c r="K22" s="72">
-        <v>0</v>
-      </c>
-      <c r="L22" s="72">
-        <v>0</v>
-      </c>
-      <c r="M22" s="72">
-        <v>0</v>
-      </c>
-      <c r="N22" s="72">
-        <v>0</v>
-      </c>
-      <c r="O22" s="72">
-        <v>0</v>
-      </c>
-      <c r="P22" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="72">
-        <v>0</v>
-      </c>
-      <c r="R22" s="72">
-        <v>0</v>
-      </c>
-      <c r="S22" s="72">
+      <c r="C22" s="71">
+        <v>0</v>
+      </c>
+      <c r="D22" s="71">
+        <v>0</v>
+      </c>
+      <c r="E22" s="71">
+        <v>0</v>
+      </c>
+      <c r="F22" s="71">
+        <v>0</v>
+      </c>
+      <c r="G22" s="71">
+        <v>0</v>
+      </c>
+      <c r="H22" s="71">
+        <v>0</v>
+      </c>
+      <c r="I22" s="71">
+        <v>0</v>
+      </c>
+      <c r="J22" s="71">
+        <v>0</v>
+      </c>
+      <c r="K22" s="71">
+        <v>0</v>
+      </c>
+      <c r="L22" s="71">
+        <v>0</v>
+      </c>
+      <c r="M22" s="71">
+        <v>0</v>
+      </c>
+      <c r="N22" s="71">
+        <v>0</v>
+      </c>
+      <c r="O22" s="71">
+        <v>0</v>
+      </c>
+      <c r="P22" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="71">
+        <v>0</v>
+      </c>
+      <c r="R22" s="71">
+        <v>0</v>
+      </c>
+      <c r="S22" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="71">
+      <c r="A23" s="93" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" s="70">
         <v>1</v>
       </c>
-      <c r="C23" s="72">
-        <v>0</v>
-      </c>
-      <c r="D23" s="72">
-        <v>0</v>
-      </c>
-      <c r="E23" s="72">
-        <v>0</v>
-      </c>
-      <c r="F23" s="72">
-        <v>0</v>
-      </c>
-      <c r="G23" s="72">
-        <v>0</v>
-      </c>
-      <c r="H23" s="72">
-        <v>0</v>
-      </c>
-      <c r="I23" s="72">
-        <v>0</v>
-      </c>
-      <c r="J23" s="72">
-        <v>0</v>
-      </c>
-      <c r="K23" s="72">
-        <v>0</v>
-      </c>
-      <c r="L23" s="72">
-        <v>0</v>
-      </c>
-      <c r="M23" s="72">
-        <v>0</v>
-      </c>
-      <c r="N23" s="72">
-        <v>0</v>
-      </c>
-      <c r="O23" s="72">
-        <v>0</v>
-      </c>
-      <c r="P23" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="72">
-        <v>0</v>
-      </c>
-      <c r="R23" s="72">
-        <v>0</v>
-      </c>
-      <c r="S23" s="72">
+      <c r="C23" s="71">
+        <v>0</v>
+      </c>
+      <c r="D23" s="71">
+        <v>0</v>
+      </c>
+      <c r="E23" s="71">
+        <v>0</v>
+      </c>
+      <c r="F23" s="71">
+        <v>0</v>
+      </c>
+      <c r="G23" s="71">
+        <v>0</v>
+      </c>
+      <c r="H23" s="71">
+        <v>0</v>
+      </c>
+      <c r="I23" s="71">
+        <v>0</v>
+      </c>
+      <c r="J23" s="71">
+        <v>0</v>
+      </c>
+      <c r="K23" s="71">
+        <v>0</v>
+      </c>
+      <c r="L23" s="71">
+        <v>0</v>
+      </c>
+      <c r="M23" s="71">
+        <v>0</v>
+      </c>
+      <c r="N23" s="71">
+        <v>0</v>
+      </c>
+      <c r="O23" s="71">
+        <v>0</v>
+      </c>
+      <c r="P23" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="71">
+        <v>0</v>
+      </c>
+      <c r="R23" s="71">
+        <v>0</v>
+      </c>
+      <c r="S23" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="71">
+      <c r="A24" s="93" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="70">
         <v>1</v>
       </c>
-      <c r="C24" s="72">
-        <v>0</v>
-      </c>
-      <c r="D24" s="72">
-        <v>0</v>
-      </c>
-      <c r="E24" s="72">
-        <v>0</v>
-      </c>
-      <c r="F24" s="72">
-        <v>0</v>
-      </c>
-      <c r="G24" s="72">
-        <v>0</v>
-      </c>
-      <c r="H24" s="72">
-        <v>0</v>
-      </c>
-      <c r="I24" s="72">
-        <v>0</v>
-      </c>
-      <c r="J24" s="72">
-        <v>0</v>
-      </c>
-      <c r="K24" s="72">
-        <v>0</v>
-      </c>
-      <c r="L24" s="72">
-        <v>0</v>
-      </c>
-      <c r="M24" s="72">
-        <v>0</v>
-      </c>
-      <c r="N24" s="72">
-        <v>0</v>
-      </c>
-      <c r="O24" s="72">
-        <v>0</v>
-      </c>
-      <c r="P24" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="72">
-        <v>0</v>
-      </c>
-      <c r="R24" s="72">
-        <v>0</v>
-      </c>
-      <c r="S24" s="72">
+      <c r="C24" s="71">
+        <v>0</v>
+      </c>
+      <c r="D24" s="71">
+        <v>0</v>
+      </c>
+      <c r="E24" s="71">
+        <v>0</v>
+      </c>
+      <c r="F24" s="71">
+        <v>0</v>
+      </c>
+      <c r="G24" s="71">
+        <v>0</v>
+      </c>
+      <c r="H24" s="71">
+        <v>0</v>
+      </c>
+      <c r="I24" s="71">
+        <v>0</v>
+      </c>
+      <c r="J24" s="71">
+        <v>0</v>
+      </c>
+      <c r="K24" s="71">
+        <v>0</v>
+      </c>
+      <c r="L24" s="71">
+        <v>0</v>
+      </c>
+      <c r="M24" s="71">
+        <v>0</v>
+      </c>
+      <c r="N24" s="71">
+        <v>0</v>
+      </c>
+      <c r="O24" s="71">
+        <v>0</v>
+      </c>
+      <c r="P24" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="71">
+        <v>0</v>
+      </c>
+      <c r="R24" s="71">
+        <v>0</v>
+      </c>
+      <c r="S24" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="71">
+      <c r="A25" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="70">
         <v>1</v>
       </c>
-      <c r="C25" s="72">
-        <v>0</v>
-      </c>
-      <c r="D25" s="72">
-        <v>0</v>
-      </c>
-      <c r="E25" s="72">
-        <v>0</v>
-      </c>
-      <c r="F25" s="72">
-        <v>0</v>
-      </c>
-      <c r="G25" s="72">
-        <v>0</v>
-      </c>
-      <c r="H25" s="72">
-        <v>0</v>
-      </c>
-      <c r="I25" s="72">
-        <v>0</v>
-      </c>
-      <c r="J25" s="72">
-        <v>0</v>
-      </c>
-      <c r="K25" s="72">
-        <v>0</v>
-      </c>
-      <c r="L25" s="72">
-        <v>0</v>
-      </c>
-      <c r="M25" s="72">
-        <v>0</v>
-      </c>
-      <c r="N25" s="72">
-        <v>0</v>
-      </c>
-      <c r="O25" s="72">
-        <v>0</v>
-      </c>
-      <c r="P25" s="72">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="72">
-        <v>0</v>
-      </c>
-      <c r="R25" s="72">
-        <v>0</v>
-      </c>
-      <c r="S25" s="72">
+      <c r="C25" s="71">
+        <v>0</v>
+      </c>
+      <c r="D25" s="71">
+        <v>0</v>
+      </c>
+      <c r="E25" s="71">
+        <v>0</v>
+      </c>
+      <c r="F25" s="71">
+        <v>0</v>
+      </c>
+      <c r="G25" s="71">
+        <v>0</v>
+      </c>
+      <c r="H25" s="71">
+        <v>0</v>
+      </c>
+      <c r="I25" s="71">
+        <v>0</v>
+      </c>
+      <c r="J25" s="71">
+        <v>0</v>
+      </c>
+      <c r="K25" s="71">
+        <v>0</v>
+      </c>
+      <c r="L25" s="71">
+        <v>0</v>
+      </c>
+      <c r="M25" s="71">
+        <v>0</v>
+      </c>
+      <c r="N25" s="71">
+        <v>0</v>
+      </c>
+      <c r="O25" s="71">
+        <v>0</v>
+      </c>
+      <c r="P25" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="71">
+        <v>0</v>
+      </c>
+      <c r="R25" s="71">
+        <v>0</v>
+      </c>
+      <c r="S25" s="71">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>7</v>
+        <v>142</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="3"/>
@@ -7099,362 +7078,362 @@
       <c r="S26" s="3"/>
     </row>
     <row r="27" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="66" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="73">
+      <c r="A27" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="72">
         <v>2</v>
       </c>
-      <c r="C27" s="74">
-        <v>0</v>
-      </c>
-      <c r="D27" s="74">
-        <v>0</v>
-      </c>
-      <c r="E27" s="74">
-        <v>0</v>
-      </c>
-      <c r="F27" s="74">
-        <v>0</v>
-      </c>
-      <c r="G27" s="74">
-        <v>0</v>
-      </c>
-      <c r="H27" s="74">
-        <v>0</v>
-      </c>
-      <c r="I27" s="74">
-        <v>0</v>
-      </c>
-      <c r="J27" s="74">
-        <v>0</v>
-      </c>
-      <c r="K27" s="74">
-        <v>0</v>
-      </c>
-      <c r="L27" s="74">
-        <v>0</v>
-      </c>
-      <c r="M27" s="74">
-        <v>0</v>
-      </c>
-      <c r="N27" s="74">
-        <v>0</v>
-      </c>
-      <c r="O27" s="74">
-        <v>0</v>
-      </c>
-      <c r="P27" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="74">
-        <v>0</v>
-      </c>
-      <c r="R27" s="74">
-        <v>0</v>
-      </c>
-      <c r="S27" s="74">
+      <c r="C27" s="73">
+        <v>0</v>
+      </c>
+      <c r="D27" s="73">
+        <v>0</v>
+      </c>
+      <c r="E27" s="73">
+        <v>0</v>
+      </c>
+      <c r="F27" s="73">
+        <v>0</v>
+      </c>
+      <c r="G27" s="73">
+        <v>0</v>
+      </c>
+      <c r="H27" s="73">
+        <v>0</v>
+      </c>
+      <c r="I27" s="73">
+        <v>0</v>
+      </c>
+      <c r="J27" s="73">
+        <v>0</v>
+      </c>
+      <c r="K27" s="73">
+        <v>0</v>
+      </c>
+      <c r="L27" s="73">
+        <v>0</v>
+      </c>
+      <c r="M27" s="73">
+        <v>0</v>
+      </c>
+      <c r="N27" s="73">
+        <v>0</v>
+      </c>
+      <c r="O27" s="73">
+        <v>0</v>
+      </c>
+      <c r="P27" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="73">
+        <v>0</v>
+      </c>
+      <c r="R27" s="73">
+        <v>0</v>
+      </c>
+      <c r="S27" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="73">
+      <c r="A28" s="94" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="72">
         <v>2</v>
       </c>
-      <c r="C28" s="74">
-        <v>0</v>
-      </c>
-      <c r="D28" s="74">
-        <v>0</v>
-      </c>
-      <c r="E28" s="74">
-        <v>0</v>
-      </c>
-      <c r="F28" s="74">
-        <v>0</v>
-      </c>
-      <c r="G28" s="74">
-        <v>0</v>
-      </c>
-      <c r="H28" s="74">
-        <v>0</v>
-      </c>
-      <c r="I28" s="74">
-        <v>0</v>
-      </c>
-      <c r="J28" s="74">
-        <v>0</v>
-      </c>
-      <c r="K28" s="74">
-        <v>0</v>
-      </c>
-      <c r="L28" s="74">
-        <v>0</v>
-      </c>
-      <c r="M28" s="74">
-        <v>0</v>
-      </c>
-      <c r="N28" s="74">
-        <v>0</v>
-      </c>
-      <c r="O28" s="74">
-        <v>0</v>
-      </c>
-      <c r="P28" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="74">
-        <v>0</v>
-      </c>
-      <c r="R28" s="74">
-        <v>0</v>
-      </c>
-      <c r="S28" s="74">
+      <c r="C28" s="73">
+        <v>0</v>
+      </c>
+      <c r="D28" s="73">
+        <v>0</v>
+      </c>
+      <c r="E28" s="73">
+        <v>0</v>
+      </c>
+      <c r="F28" s="73">
+        <v>0</v>
+      </c>
+      <c r="G28" s="73">
+        <v>0</v>
+      </c>
+      <c r="H28" s="73">
+        <v>0</v>
+      </c>
+      <c r="I28" s="73">
+        <v>0</v>
+      </c>
+      <c r="J28" s="73">
+        <v>0</v>
+      </c>
+      <c r="K28" s="73">
+        <v>0</v>
+      </c>
+      <c r="L28" s="73">
+        <v>0</v>
+      </c>
+      <c r="M28" s="73">
+        <v>0</v>
+      </c>
+      <c r="N28" s="73">
+        <v>0</v>
+      </c>
+      <c r="O28" s="73">
+        <v>0</v>
+      </c>
+      <c r="P28" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="73">
+        <v>0</v>
+      </c>
+      <c r="R28" s="73">
+        <v>0</v>
+      </c>
+      <c r="S28" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="73">
+      <c r="A29" s="94" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="72">
         <v>1</v>
       </c>
-      <c r="C29" s="74">
-        <v>0</v>
-      </c>
-      <c r="D29" s="74">
-        <v>0</v>
-      </c>
-      <c r="E29" s="74">
-        <v>0</v>
-      </c>
-      <c r="F29" s="74">
-        <v>0</v>
-      </c>
-      <c r="G29" s="74">
-        <v>0</v>
-      </c>
-      <c r="H29" s="74">
-        <v>0</v>
-      </c>
-      <c r="I29" s="74">
-        <v>0</v>
-      </c>
-      <c r="J29" s="74">
-        <v>0</v>
-      </c>
-      <c r="K29" s="74">
-        <v>0</v>
-      </c>
-      <c r="L29" s="74">
-        <v>0</v>
-      </c>
-      <c r="M29" s="74">
-        <v>0</v>
-      </c>
-      <c r="N29" s="74">
-        <v>0</v>
-      </c>
-      <c r="O29" s="74">
-        <v>0</v>
-      </c>
-      <c r="P29" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="74">
-        <v>0</v>
-      </c>
-      <c r="R29" s="74">
-        <v>0</v>
-      </c>
-      <c r="S29" s="74">
+      <c r="C29" s="73">
+        <v>0</v>
+      </c>
+      <c r="D29" s="73">
+        <v>0</v>
+      </c>
+      <c r="E29" s="73">
+        <v>0</v>
+      </c>
+      <c r="F29" s="73">
+        <v>0</v>
+      </c>
+      <c r="G29" s="73">
+        <v>0</v>
+      </c>
+      <c r="H29" s="73">
+        <v>0</v>
+      </c>
+      <c r="I29" s="73">
+        <v>0</v>
+      </c>
+      <c r="J29" s="73">
+        <v>0</v>
+      </c>
+      <c r="K29" s="73">
+        <v>0</v>
+      </c>
+      <c r="L29" s="73">
+        <v>0</v>
+      </c>
+      <c r="M29" s="73">
+        <v>0</v>
+      </c>
+      <c r="N29" s="73">
+        <v>0</v>
+      </c>
+      <c r="O29" s="73">
+        <v>0</v>
+      </c>
+      <c r="P29" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="73">
+        <v>0</v>
+      </c>
+      <c r="R29" s="73">
+        <v>0</v>
+      </c>
+      <c r="S29" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="73">
+      <c r="A30" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="72">
         <v>1</v>
       </c>
-      <c r="C30" s="74">
-        <v>0</v>
-      </c>
-      <c r="D30" s="74">
-        <v>0</v>
-      </c>
-      <c r="E30" s="74">
-        <v>0</v>
-      </c>
-      <c r="F30" s="74">
-        <v>0</v>
-      </c>
-      <c r="G30" s="74">
-        <v>0</v>
-      </c>
-      <c r="H30" s="74">
-        <v>0</v>
-      </c>
-      <c r="I30" s="74">
-        <v>0</v>
-      </c>
-      <c r="J30" s="74">
-        <v>0</v>
-      </c>
-      <c r="K30" s="74">
-        <v>0</v>
-      </c>
-      <c r="L30" s="74">
-        <v>0</v>
-      </c>
-      <c r="M30" s="74">
-        <v>0</v>
-      </c>
-      <c r="N30" s="74">
-        <v>0</v>
-      </c>
-      <c r="O30" s="74">
-        <v>0</v>
-      </c>
-      <c r="P30" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="74">
-        <v>0</v>
-      </c>
-      <c r="R30" s="74">
-        <v>0</v>
-      </c>
-      <c r="S30" s="74">
+      <c r="C30" s="73">
+        <v>0</v>
+      </c>
+      <c r="D30" s="73">
+        <v>0</v>
+      </c>
+      <c r="E30" s="73">
+        <v>0</v>
+      </c>
+      <c r="F30" s="73">
+        <v>0</v>
+      </c>
+      <c r="G30" s="73">
+        <v>0</v>
+      </c>
+      <c r="H30" s="73">
+        <v>0</v>
+      </c>
+      <c r="I30" s="73">
+        <v>0</v>
+      </c>
+      <c r="J30" s="73">
+        <v>0</v>
+      </c>
+      <c r="K30" s="73">
+        <v>0</v>
+      </c>
+      <c r="L30" s="73">
+        <v>0</v>
+      </c>
+      <c r="M30" s="73">
+        <v>0</v>
+      </c>
+      <c r="N30" s="73">
+        <v>0</v>
+      </c>
+      <c r="O30" s="73">
+        <v>0</v>
+      </c>
+      <c r="P30" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="73">
+        <v>0</v>
+      </c>
+      <c r="R30" s="73">
+        <v>0</v>
+      </c>
+      <c r="S30" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="66" t="s">
-        <v>64</v>
-      </c>
-      <c r="B31" s="73">
+      <c r="A31" s="94" t="s">
+        <v>146</v>
+      </c>
+      <c r="B31" s="72">
         <v>1</v>
       </c>
-      <c r="C31" s="74">
-        <v>0</v>
-      </c>
-      <c r="D31" s="74">
-        <v>0</v>
-      </c>
-      <c r="E31" s="74">
-        <v>0</v>
-      </c>
-      <c r="F31" s="74">
-        <v>0</v>
-      </c>
-      <c r="G31" s="74">
-        <v>0</v>
-      </c>
-      <c r="H31" s="74">
-        <v>0</v>
-      </c>
-      <c r="I31" s="74">
-        <v>0</v>
-      </c>
-      <c r="J31" s="74">
-        <v>0</v>
-      </c>
-      <c r="K31" s="74">
-        <v>0</v>
-      </c>
-      <c r="L31" s="74">
-        <v>0</v>
-      </c>
-      <c r="M31" s="74">
-        <v>0</v>
-      </c>
-      <c r="N31" s="74">
-        <v>0</v>
-      </c>
-      <c r="O31" s="74">
-        <v>0</v>
-      </c>
-      <c r="P31" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="74">
-        <v>0</v>
-      </c>
-      <c r="R31" s="74">
-        <v>0</v>
-      </c>
-      <c r="S31" s="74">
+      <c r="C31" s="73">
+        <v>0</v>
+      </c>
+      <c r="D31" s="73">
+        <v>0</v>
+      </c>
+      <c r="E31" s="73">
+        <v>0</v>
+      </c>
+      <c r="F31" s="73">
+        <v>0</v>
+      </c>
+      <c r="G31" s="73">
+        <v>0</v>
+      </c>
+      <c r="H31" s="73">
+        <v>0</v>
+      </c>
+      <c r="I31" s="73">
+        <v>0</v>
+      </c>
+      <c r="J31" s="73">
+        <v>0</v>
+      </c>
+      <c r="K31" s="73">
+        <v>0</v>
+      </c>
+      <c r="L31" s="73">
+        <v>0</v>
+      </c>
+      <c r="M31" s="73">
+        <v>0</v>
+      </c>
+      <c r="N31" s="73">
+        <v>0</v>
+      </c>
+      <c r="O31" s="73">
+        <v>0</v>
+      </c>
+      <c r="P31" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="73">
+        <v>0</v>
+      </c>
+      <c r="R31" s="73">
+        <v>0</v>
+      </c>
+      <c r="S31" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="72">
+        <v>1</v>
+      </c>
+      <c r="C32" s="73">
+        <v>0</v>
+      </c>
+      <c r="D32" s="73">
+        <v>0</v>
+      </c>
+      <c r="E32" s="73">
+        <v>0</v>
+      </c>
+      <c r="F32" s="73">
+        <v>0</v>
+      </c>
+      <c r="G32" s="73">
+        <v>0</v>
+      </c>
+      <c r="H32" s="73">
+        <v>0</v>
+      </c>
+      <c r="I32" s="73">
+        <v>0</v>
+      </c>
+      <c r="J32" s="73">
+        <v>0</v>
+      </c>
+      <c r="K32" s="73">
+        <v>0</v>
+      </c>
+      <c r="L32" s="73">
+        <v>0</v>
+      </c>
+      <c r="M32" s="73">
+        <v>0</v>
+      </c>
+      <c r="N32" s="73">
+        <v>0</v>
+      </c>
+      <c r="O32" s="73">
+        <v>0</v>
+      </c>
+      <c r="P32" s="73">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="73">
+        <v>0</v>
+      </c>
+      <c r="R32" s="73">
+        <v>0</v>
+      </c>
+      <c r="S32" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="76" t="s">
         <v>12</v>
-      </c>
-      <c r="B32" s="73">
-        <v>1</v>
-      </c>
-      <c r="C32" s="74">
-        <v>0</v>
-      </c>
-      <c r="D32" s="74">
-        <v>0</v>
-      </c>
-      <c r="E32" s="74">
-        <v>0</v>
-      </c>
-      <c r="F32" s="74">
-        <v>0</v>
-      </c>
-      <c r="G32" s="74">
-        <v>0</v>
-      </c>
-      <c r="H32" s="74">
-        <v>0</v>
-      </c>
-      <c r="I32" s="74">
-        <v>0</v>
-      </c>
-      <c r="J32" s="74">
-        <v>0</v>
-      </c>
-      <c r="K32" s="74">
-        <v>0</v>
-      </c>
-      <c r="L32" s="74">
-        <v>0</v>
-      </c>
-      <c r="M32" s="74">
-        <v>0</v>
-      </c>
-      <c r="N32" s="74">
-        <v>0</v>
-      </c>
-      <c r="O32" s="74">
-        <v>0</v>
-      </c>
-      <c r="P32" s="74">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="74">
-        <v>0</v>
-      </c>
-      <c r="R32" s="74">
-        <v>0</v>
-      </c>
-      <c r="S32" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="77" t="s">
-        <v>13</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="3"/>
@@ -7476,135 +7455,135 @@
       <c r="S33" s="3"/>
     </row>
     <row r="34" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="78" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" s="67">
+      <c r="A34" s="95" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="66">
         <v>1</v>
       </c>
-      <c r="C34" s="68">
-        <v>0</v>
-      </c>
-      <c r="D34" s="68">
-        <v>0</v>
-      </c>
-      <c r="E34" s="68">
-        <v>0</v>
-      </c>
-      <c r="F34" s="68">
-        <v>0</v>
-      </c>
-      <c r="G34" s="68">
-        <v>0</v>
-      </c>
-      <c r="H34" s="68">
-        <v>0</v>
-      </c>
-      <c r="I34" s="68">
-        <v>0</v>
-      </c>
-      <c r="J34" s="68">
-        <v>0</v>
-      </c>
-      <c r="K34" s="68">
-        <v>0</v>
-      </c>
-      <c r="L34" s="68">
-        <v>0</v>
-      </c>
-      <c r="M34" s="68">
-        <v>0</v>
-      </c>
-      <c r="N34" s="68">
-        <v>0</v>
-      </c>
-      <c r="O34" s="68">
-        <v>0</v>
-      </c>
-      <c r="P34" s="68">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="68">
-        <v>0</v>
-      </c>
-      <c r="R34" s="68">
-        <v>0</v>
-      </c>
-      <c r="S34" s="68">
+      <c r="C34" s="67">
+        <v>0</v>
+      </c>
+      <c r="D34" s="67">
+        <v>0</v>
+      </c>
+      <c r="E34" s="67">
+        <v>0</v>
+      </c>
+      <c r="F34" s="67">
+        <v>0</v>
+      </c>
+      <c r="G34" s="67">
+        <v>0</v>
+      </c>
+      <c r="H34" s="67">
+        <v>0</v>
+      </c>
+      <c r="I34" s="67">
+        <v>0</v>
+      </c>
+      <c r="J34" s="67">
+        <v>0</v>
+      </c>
+      <c r="K34" s="67">
+        <v>0</v>
+      </c>
+      <c r="L34" s="67">
+        <v>0</v>
+      </c>
+      <c r="M34" s="67">
+        <v>0</v>
+      </c>
+      <c r="N34" s="67">
+        <v>0</v>
+      </c>
+      <c r="O34" s="67">
+        <v>0</v>
+      </c>
+      <c r="P34" s="67">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="67">
+        <v>0</v>
+      </c>
+      <c r="R34" s="67">
+        <v>0</v>
+      </c>
+      <c r="S34" s="67">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="75"/>
-      <c r="B35" s="76">
+      <c r="A35" s="74"/>
+      <c r="B35" s="75">
         <f>SUM(B3:B34)</f>
         <v>40</v>
       </c>
-      <c r="C35" s="76">
+      <c r="C35" s="75">
         <f t="shared" ref="C35:S35" si="0">SUM(C3:C34)</f>
         <v>0</v>
       </c>
-      <c r="D35" s="76">
+      <c r="D35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E35" s="76">
+      <c r="E35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F35" s="76">
+      <c r="F35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G35" s="76">
+      <c r="G35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H35" s="76">
+      <c r="H35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="76">
+      <c r="I35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="76">
+      <c r="J35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K35" s="76">
+      <c r="K35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L35" s="76">
+      <c r="L35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M35" s="76">
+      <c r="M35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N35" s="76">
+      <c r="N35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O35" s="76">
+      <c r="O35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P35" s="76">
+      <c r="P35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q35" s="76">
+      <c r="Q35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R35" s="76">
+      <c r="R35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S35" s="76">
+      <c r="S35" s="75">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -8587,37 +8566,37 @@
     <row r="1" spans="1:25" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A1" s="20"/>
       <c r="B1" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="E1" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G1" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="H1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="I1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="J1" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="K1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>25</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>26</v>
       </c>
       <c r="M1" s="26"/>
       <c r="N1" s="26"/>
@@ -8635,10 +8614,10 @@
     </row>
     <row r="2" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C2" s="30">
         <v>30</v>
@@ -8688,10 +8667,10 @@
     </row>
     <row r="3" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C3" s="30">
         <v>30</v>
@@ -8741,10 +8720,10 @@
     </row>
     <row r="4" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="C4" s="30">
         <v>30</v>
@@ -8794,10 +8773,10 @@
     </row>
     <row r="5" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C5" s="30">
         <v>30</v>
@@ -8847,10 +8826,10 @@
     </row>
     <row r="6" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="C6" s="30">
         <v>30</v>
@@ -8900,10 +8879,10 @@
     </row>
     <row r="7" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="C7" s="30">
         <v>30</v>
@@ -8953,10 +8932,10 @@
     </row>
     <row r="8" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="C8" s="30">
         <v>30</v>
@@ -9006,10 +8985,10 @@
     </row>
     <row r="9" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="C9" s="30">
         <v>30</v>
@@ -9059,10 +9038,10 @@
     </row>
     <row r="10" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="C10" s="30">
         <v>30</v>
@@ -9112,10 +9091,10 @@
     </row>
     <row r="11" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C11" s="30">
         <v>30</v>
@@ -9165,10 +9144,10 @@
     </row>
     <row r="12" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C12" s="30">
         <v>30</v>
@@ -9218,10 +9197,10 @@
     </row>
     <row r="13" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C13" s="30">
         <v>30</v>
@@ -9271,10 +9250,10 @@
     </row>
     <row r="14" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="C14" s="30">
         <v>30</v>
@@ -9324,10 +9303,10 @@
     </row>
     <row r="15" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C15" s="30">
         <v>30</v>
@@ -9377,10 +9356,10 @@
     </row>
     <row r="16" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C16" s="30">
         <v>30</v>
@@ -9430,10 +9409,10 @@
     </row>
     <row r="17" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="C17" s="30">
         <v>30</v>
@@ -9483,10 +9462,10 @@
     </row>
     <row r="18" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="28" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="C18" s="30">
         <v>30</v>
@@ -9567,7 +9546,7 @@
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
       <c r="E20" s="39" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20" s="38">
         <v>1</v>
@@ -9598,7 +9577,7 @@
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
       <c r="E21" s="40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21" s="38">
         <v>2</v>
@@ -9629,7 +9608,7 @@
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
       <c r="E22" s="40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F22" s="38">
         <v>3</v>
@@ -9660,7 +9639,7 @@
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
       <c r="E23" s="40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F23" s="38">
         <v>4</v>
@@ -9691,7 +9670,7 @@
       <c r="C24" s="37"/>
       <c r="D24" s="37"/>
       <c r="E24" s="40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F24" s="38">
         <v>5</v>

--- a/javitolap.xlsx
+++ b/javitolap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Peter\Desktop\2026_alapvizsga\2026_alapvizsga_eles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D160FC8-90C9-4FE9-B460-0CFEE5E9B1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D75D280-CA12-40D5-B956-B10B14FB3191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -474,16 +474,10 @@
     <t>A 4 PC és a SZERVER számára helyes alapértelmezett átjárót állított be.</t>
   </si>
   <si>
-    <t>A 4 PC és a SZERVER számára helyes DNS kiszolgáló címet állított be. 13.13.13.13</t>
-  </si>
-  <si>
     <t>Az IGAZGATO_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
   </si>
   <si>
     <t>Az ORVOS_RT forgalomirányító összes interfészén az IP-címet és az alhálózati maszkot jól beállította.</t>
-  </si>
-  <si>
-    <t>A SHOP_WIFI eszköz internet portján megfelelő IP-címet, alhálózati maszkot, alapértelmezett átjárót és DNS kiszolgáló címet állított be. 172.30.0.3  255.255.0.0.   172.30.0.1  13.13.13.13</t>
   </si>
   <si>
     <r>
@@ -658,6 +652,12 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>A 4 PC és a SZERVER számára helyes DNS kiszolgáló címet állított be. 4.4.4.4</t>
+  </si>
+  <si>
+    <t>A SHOP_WIFI eszköz internet portján megfelelő IP-címet, alhálózati maszkot, alapértelmezett átjárót és DNS kiszolgáló címet állított be. 172.30.0.3  255.255.0.0.   172.30.0.1  4.4.4.4</t>
   </si>
 </sst>
 </file>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" s="68">
         <v>2</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="11" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="91" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B11" s="68">
         <v>2</v>
@@ -6502,7 +6502,7 @@
     </row>
     <row r="16" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="91" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="B16" s="68">
         <v>1</v>
@@ -6561,7 +6561,7 @@
     </row>
     <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="91" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B17" s="68">
         <v>4</v>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="21" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="92" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B21" s="70">
         <v>1</v>
@@ -6820,7 +6820,7 @@
     </row>
     <row r="22" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B22" s="70">
         <v>1</v>
@@ -6879,7 +6879,7 @@
     </row>
     <row r="23" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B23" s="70">
         <v>1</v>
@@ -6938,7 +6938,7 @@
     </row>
     <row r="24" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B24" s="70">
         <v>1</v>
@@ -6997,7 +6997,7 @@
     </row>
     <row r="25" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B25" s="70">
         <v>1</v>
@@ -7056,7 +7056,7 @@
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="3"/>
@@ -7079,7 +7079,7 @@
     </row>
     <row r="27" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B27" s="72">
         <v>2</v>
@@ -7138,7 +7138,7 @@
     </row>
     <row r="28" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B28" s="72">
         <v>2</v>
@@ -7197,7 +7197,7 @@
     </row>
     <row r="29" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B29" s="72">
         <v>1</v>
@@ -7256,7 +7256,7 @@
     </row>
     <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B30" s="72">
         <v>1</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="31" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B31" s="72">
         <v>1</v>
@@ -7456,7 +7456,7 @@
     </row>
     <row r="34" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="95" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B34" s="66">
         <v>1</v>

--- a/javitolap.xlsx
+++ b/javitolap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Peter\Desktop\2026_alapvizsga\2026_alapvizsga_eles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D75D280-CA12-40D5-B956-B10B14FB3191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D84A44F-3EC2-4E03-A315-C8411589C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Webprogramozas" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="148">
   <si>
     <t>A megoldás mentése, eszközök elhelyezése</t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>Bootstrap css állomány beimportálása</t>
-  </si>
-  <si>
-    <t>5.</t>
   </si>
   <si>
     <t>6.</t>
@@ -1918,28 +1915,62 @@
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="79" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="49">
         <v>1</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="57"/>
-      <c r="S7" s="50"/>
+      <c r="C7" s="50">
+        <v>0</v>
+      </c>
+      <c r="D7" s="50">
+        <v>0</v>
+      </c>
+      <c r="E7" s="57">
+        <v>0</v>
+      </c>
+      <c r="F7" s="57">
+        <v>0</v>
+      </c>
+      <c r="G7" s="57">
+        <v>0</v>
+      </c>
+      <c r="H7" s="57">
+        <v>0</v>
+      </c>
+      <c r="I7" s="57">
+        <v>0</v>
+      </c>
+      <c r="J7" s="57">
+        <v>0</v>
+      </c>
+      <c r="K7" s="57">
+        <v>0</v>
+      </c>
+      <c r="L7" s="57">
+        <v>0</v>
+      </c>
+      <c r="M7" s="57">
+        <v>0</v>
+      </c>
+      <c r="N7" s="57">
+        <v>0</v>
+      </c>
+      <c r="O7" s="57">
+        <v>0</v>
+      </c>
+      <c r="P7" s="57">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="57">
+        <v>0</v>
+      </c>
+      <c r="R7" s="57">
+        <v>0</v>
+      </c>
+      <c r="S7" s="50">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
@@ -2061,7 +2092,7 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="49">
         <v>1</v>
@@ -2120,7 +2151,7 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" s="52">
         <v>1</v>
@@ -2238,7 +2269,7 @@
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B13" s="49">
         <v>1</v>
@@ -2297,7 +2328,7 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="79" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="49">
         <v>1</v>
@@ -2415,7 +2446,7 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="49">
         <v>1</v>
@@ -2474,7 +2505,7 @@
     </row>
     <row r="17" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="55">
         <v>1</v>
@@ -2533,7 +2564,7 @@
     </row>
     <row r="18" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B18" s="55">
         <v>1</v>
@@ -2592,7 +2623,7 @@
     </row>
     <row r="19" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="55">
         <v>1</v>
@@ -2651,7 +2682,7 @@
     </row>
     <row r="20" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B20" s="55">
         <v>1</v>
@@ -2710,7 +2741,7 @@
     </row>
     <row r="21" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B21" s="55">
         <v>1</v>
@@ -2769,7 +2800,7 @@
     </row>
     <row r="22" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B22" s="55">
         <v>2</v>
@@ -2828,7 +2859,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="49">
         <v>1</v>
@@ -2887,7 +2918,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B24" s="49">
         <v>1</v>
@@ -2946,7 +2977,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="53" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B25" s="52">
         <v>1</v>
@@ -3005,7 +3036,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B26" s="52">
         <v>1</v>
@@ -3064,7 +3095,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B27" s="52">
         <v>2</v>
@@ -3123,7 +3154,7 @@
     </row>
     <row r="28" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B28" s="49">
         <v>1</v>
@@ -3182,7 +3213,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="49">
         <v>1</v>
@@ -3241,7 +3272,7 @@
     </row>
     <row r="30" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B30" s="55">
         <v>1</v>
@@ -3300,7 +3331,7 @@
     </row>
     <row r="31" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B31" s="55">
         <v>1</v>
@@ -3359,7 +3390,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" s="52">
         <v>1</v>
@@ -3418,7 +3449,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="79" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="77">
         <v>1</v>
@@ -3477,7 +3508,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="79" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B34" s="77">
         <v>1</v>
@@ -3536,7 +3567,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B35" s="77">
         <v>1</v>
@@ -3595,7 +3626,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="80" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B36" s="58">
         <v>1</v>
@@ -3654,7 +3685,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B37" s="56">
         <v>2</v>
@@ -3713,7 +3744,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" s="43">
         <v>1</v>
@@ -3920,10 +3951,10 @@
     </row>
     <row r="2" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B2" s="83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C2" s="12">
         <v>0</v>
@@ -3982,7 +4013,7 @@
         <v>38</v>
       </c>
       <c r="B3" s="83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="12">
         <v>0</v>
@@ -4041,7 +4072,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -4100,7 +4131,7 @@
         <v>39</v>
       </c>
       <c r="B5" s="83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -4156,10 +4187,10 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="82" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -4218,7 +4249,7 @@
         <v>41</v>
       </c>
       <c r="B7" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -4274,10 +4305,10 @@
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="88" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -4333,10 +4364,10 @@
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="18">
         <v>0</v>
@@ -4392,10 +4423,10 @@
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="18">
         <v>0</v>
@@ -4451,10 +4482,10 @@
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" s="18">
         <v>0</v>
@@ -4510,10 +4541,10 @@
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12" s="18">
         <v>0</v>
@@ -4569,10 +4600,10 @@
     </row>
     <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -4628,10 +4659,10 @@
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -4687,10 +4718,10 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -4746,10 +4777,10 @@
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -4808,7 +4839,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -4864,10 +4895,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -4923,10 +4954,10 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="89" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C19" s="19">
         <v>0</v>
@@ -4985,7 +5016,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -5041,10 +5072,10 @@
     </row>
     <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -5100,10 +5131,10 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -5162,7 +5193,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -5218,10 +5249,10 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="19">
         <v>0</v>
@@ -5277,10 +5308,10 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C25" s="19">
         <v>0</v>
@@ -5336,10 +5367,10 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C26" s="19">
         <v>0</v>
@@ -5395,10 +5426,10 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B27" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
@@ -5454,10 +5485,10 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B28" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
@@ -5513,10 +5544,10 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -5538,10 +5569,10 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
@@ -5771,7 +5802,7 @@
     </row>
     <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B3" s="61">
         <v>1</v>
@@ -6089,7 +6120,7 @@
     </row>
     <row r="9" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="91" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B9" s="68">
         <v>3</v>
@@ -6148,7 +6179,7 @@
     </row>
     <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B10" s="68">
         <v>2</v>
@@ -6207,7 +6238,7 @@
     </row>
     <row r="11" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="91" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B11" s="68">
         <v>2</v>
@@ -6266,7 +6297,7 @@
     </row>
     <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B12" s="68">
         <v>1</v>
@@ -6325,7 +6356,7 @@
     </row>
     <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="91" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B13" s="68">
         <v>1</v>
@@ -6384,7 +6415,7 @@
     </row>
     <row r="14" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="91" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B14" s="68">
         <v>4</v>
@@ -6443,7 +6474,7 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="91" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" s="68">
         <v>1</v>
@@ -6502,7 +6533,7 @@
     </row>
     <row r="16" spans="1:24" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="91" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B16" s="68">
         <v>1</v>
@@ -6561,7 +6592,7 @@
     </row>
     <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="91" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" s="68">
         <v>4</v>
@@ -6761,7 +6792,7 @@
     </row>
     <row r="21" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="92" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B21" s="70">
         <v>1</v>
@@ -6820,7 +6851,7 @@
     </row>
     <row r="22" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B22" s="70">
         <v>1</v>
@@ -6879,7 +6910,7 @@
     </row>
     <row r="23" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23" s="70">
         <v>1</v>
@@ -6938,7 +6969,7 @@
     </row>
     <row r="24" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B24" s="70">
         <v>1</v>
@@ -6997,7 +7028,7 @@
     </row>
     <row r="25" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B25" s="70">
         <v>1</v>
@@ -7056,7 +7087,7 @@
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="3"/>
@@ -7079,7 +7110,7 @@
     </row>
     <row r="27" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B27" s="72">
         <v>2</v>
@@ -7138,7 +7169,7 @@
     </row>
     <row r="28" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B28" s="72">
         <v>2</v>
@@ -7197,7 +7228,7 @@
     </row>
     <row r="29" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B29" s="72">
         <v>1</v>
@@ -7256,7 +7287,7 @@
     </row>
     <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B30" s="72">
         <v>1</v>
@@ -7315,7 +7346,7 @@
     </row>
     <row r="31" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B31" s="72">
         <v>1</v>
@@ -7456,7 +7487,7 @@
     </row>
     <row r="34" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="95" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B34" s="66">
         <v>1</v>
@@ -8545,7 +8576,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEA57977-8E82-443D-B949-8C9E22543A50}">
-  <dimension ref="A1:Y999"/>
+  <dimension ref="A1:Y998"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.85546875" customWidth="1"/>
@@ -8626,7 +8657,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="31">
-        <f t="shared" ref="E2:E18" si="0">D2/C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2/C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="32">
@@ -8639,11 +8670,11 @@
         <v>0</v>
       </c>
       <c r="I2" s="30">
-        <f t="shared" ref="I2:I18" si="1">SUM(F2:H2)</f>
+        <f t="shared" ref="I2:I17" si="1">SUM(F2:H2)</f>
         <v>0</v>
       </c>
       <c r="J2" s="34">
-        <f t="shared" ref="J2:J18" si="2">I2/120</f>
+        <f t="shared" ref="J2:J17" si="2">I2/120</f>
         <v>0</v>
       </c>
       <c r="K2" s="35">
@@ -8700,7 +8731,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="35">
-        <f t="shared" ref="K3:K17" si="3">E3*0.1+J3*0.9</f>
+        <f t="shared" ref="K3:K16" si="3">E3*0.1+J3*0.9</f>
         <v>0</v>
       </c>
       <c r="L3" s="36"/>
@@ -8829,7 +8860,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" s="30">
         <v>30</v>
@@ -8882,7 +8913,7 @@
         <v>63</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="30">
         <v>30</v>
@@ -8935,7 +8966,7 @@
         <v>64</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="30">
         <v>30</v>
@@ -8988,7 +9019,7 @@
         <v>65</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="30">
         <v>30</v>
@@ -9041,7 +9072,7 @@
         <v>66</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" s="30">
         <v>30</v>
@@ -9094,7 +9125,7 @@
         <v>67</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C11" s="30">
         <v>30</v>
@@ -9147,7 +9178,7 @@
         <v>68</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12" s="30">
         <v>30</v>
@@ -9200,7 +9231,7 @@
         <v>69</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C13" s="30">
         <v>30</v>
@@ -9253,7 +9284,7 @@
         <v>70</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="30">
         <v>30</v>
@@ -9306,7 +9337,7 @@
         <v>71</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="30">
         <v>30</v>
@@ -9359,7 +9390,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C16" s="30">
         <v>30</v>
@@ -9412,7 +9443,7 @@
         <v>73</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="30">
         <v>30</v>
@@ -9442,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="35">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="K17" si="4">E17*0.1+J17*0.9</f>
         <v>0</v>
       </c>
       <c r="L17" s="36"/>
@@ -9460,45 +9491,19 @@
       <c r="X17" s="7"/>
       <c r="Y17" s="7"/>
     </row>
-    <row r="18" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="30">
-        <v>30</v>
-      </c>
-      <c r="D18" s="30">
-        <v>0</v>
-      </c>
-      <c r="E18" s="31">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="G18" s="30">
-        <v>0</v>
-      </c>
-      <c r="H18" s="33">
-        <v>0</v>
-      </c>
-      <c r="I18" s="30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="34">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="35">
-        <f t="shared" ref="K18" si="4">E18*0.1+J18*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="36"/>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" s="37"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="37"/>
       <c r="M18" s="37"/>
       <c r="N18" s="37"/>
       <c r="O18" s="37"/>
@@ -9513,13 +9518,17 @@
       <c r="X18" s="7"/>
       <c r="Y18" s="7"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37"/>
       <c r="B19" s="37"/>
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
+      <c r="E19" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="38">
+        <v>1</v>
+      </c>
       <c r="G19" s="37"/>
       <c r="H19" s="37"/>
       <c r="I19" s="37"/>
@@ -9545,11 +9554,11 @@
       <c r="B20" s="37"/>
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
-      <c r="E20" s="39" t="s">
-        <v>30</v>
+      <c r="E20" s="40" t="s">
+        <v>31</v>
       </c>
       <c r="F20" s="38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="37"/>
       <c r="H20" s="37"/>
@@ -9577,10 +9586,10 @@
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
       <c r="E21" s="40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37"/>
@@ -9608,10 +9617,10 @@
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
       <c r="E22" s="40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F22" s="38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37"/>
@@ -9639,10 +9648,10 @@
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
       <c r="E23" s="40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F23" s="38">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="37"/>
       <c r="H23" s="37"/>
@@ -9664,17 +9673,13 @@
       <c r="X23" s="7"/>
       <c r="Y23" s="7"/>
     </row>
-    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37"/>
       <c r="B24" s="37"/>
       <c r="C24" s="37"/>
       <c r="D24" s="37"/>
-      <c r="E24" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="38">
-        <v>5</v>
-      </c>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
       <c r="G24" s="37"/>
       <c r="H24" s="37"/>
       <c r="I24" s="37"/>
@@ -10101,26 +10106,26 @@
       <c r="Y39" s="7"/>
     </row>
     <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
-      <c r="B40" s="37"/>
-      <c r="C40" s="37"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37"/>
-      <c r="J40" s="37"/>
-      <c r="K40" s="37"/>
-      <c r="L40" s="37"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="37"/>
-      <c r="Q40" s="37"/>
-      <c r="R40" s="37"/>
-      <c r="S40" s="37"/>
-      <c r="T40" s="37"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
       <c r="U40" s="7"/>
       <c r="V40" s="7"/>
       <c r="W40" s="7"/>
@@ -10425,26 +10430,6 @@
       <c r="Y51" s="7"/>
     </row>
     <row r="52" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
       <c r="U52" s="7"/>
       <c r="V52" s="7"/>
       <c r="W52" s="7"/>
@@ -11326,13 +11311,7 @@
       <c r="X177" s="7"/>
       <c r="Y177" s="7"/>
     </row>
-    <row r="178" spans="21:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="U178" s="7"/>
-      <c r="V178" s="7"/>
-      <c r="W178" s="7"/>
-      <c r="X178" s="7"/>
-      <c r="Y178" s="7"/>
-    </row>
+    <row r="178" spans="21:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="179" spans="21:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="180" spans="21:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="181" spans="21:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12153,7 +12132,6 @@
     <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/javitolap.xlsx
+++ b/javitolap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Peter\Desktop\2026_alapvizsga\2026_alapvizsga_eles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D84A44F-3EC2-4E03-A315-C8411589C772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3087B41-0D5C-4708-8C65-AF370B5845F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Webprogramozas" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
   <si>
     <t>A megoldás mentése, eszközök elhelyezése</t>
   </si>
@@ -198,9 +198,6 @@
     <t>Bozóki Benedek Varsány</t>
   </si>
   <si>
-    <t>Búza Leonárd</t>
-  </si>
-  <si>
     <t>Dunai Sándor Erik</t>
   </si>
   <si>
@@ -271,9 +268,6 @@
   </si>
   <si>
     <t>16.</t>
-  </si>
-  <si>
-    <t>17.</t>
   </si>
   <si>
     <t>Az oldal reszponzív</t>
@@ -655,6 +649,9 @@
   </si>
   <si>
     <t>A SHOP_WIFI eszköz internet portján megfelelő IP-címet, alhálózati maszkot, alapértelmezett átjárót és DNS kiszolgáló címet állított be. 172.30.0.3  255.255.0.0.   172.30.0.1  4.4.4.4</t>
+  </si>
+  <si>
+    <t>5.</t>
   </si>
 </sst>
 </file>
@@ -1551,15 +1548,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E3FDB0-7D37-4D6D-997A-6219C9CD2D62}">
-  <dimension ref="A1:X39"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="52.140625" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="19" width="9.140625" customWidth="1"/>
+    <col min="3" max="18" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
@@ -1590,13 +1587,13 @@
         <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="N1" s="41" t="s">
-        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
         <v>56</v>
@@ -1610,17 +1607,14 @@
       <c r="R1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="41" t="s">
-        <v>60</v>
-      </c>
+      <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="43">
         <v>1</v>
@@ -1673,11 +1667,8 @@
       <c r="R2" s="44">
         <v>0</v>
       </c>
-      <c r="S2" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
         <v>35</v>
       </c>
@@ -1729,14 +1720,11 @@
       <c r="Q3" s="44">
         <v>0</v>
       </c>
-      <c r="R3" s="44">
-        <v>0</v>
-      </c>
-      <c r="S3" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R3" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="48" t="s">
         <v>7</v>
       </c>
@@ -1788,14 +1776,11 @@
       <c r="Q4" s="57">
         <v>0</v>
       </c>
-      <c r="R4" s="57">
-        <v>0</v>
-      </c>
-      <c r="S4" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R4" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
         <v>8</v>
       </c>
@@ -1847,14 +1832,11 @@
       <c r="Q5" s="57">
         <v>0</v>
       </c>
-      <c r="R5" s="57">
-        <v>0</v>
-      </c>
-      <c r="S5" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R5" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="s">
         <v>9</v>
       </c>
@@ -1906,16 +1888,13 @@
       <c r="Q6" s="57">
         <v>0</v>
       </c>
-      <c r="R6" s="57">
-        <v>0</v>
-      </c>
-      <c r="S6" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R6" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="79" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="49">
         <v>1</v>
@@ -1965,14 +1944,11 @@
       <c r="Q7" s="57">
         <v>0</v>
       </c>
-      <c r="R7" s="57">
-        <v>0</v>
-      </c>
-      <c r="S7" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R7" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="51" t="s">
         <v>10</v>
       </c>
@@ -2024,14 +2000,11 @@
       <c r="Q8" s="44">
         <v>0</v>
       </c>
-      <c r="R8" s="44">
-        <v>0</v>
-      </c>
-      <c r="S8" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R8" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="53" t="s">
         <v>13</v>
       </c>
@@ -2083,16 +2056,13 @@
       <c r="Q9" s="44">
         <v>0</v>
       </c>
-      <c r="R9" s="44">
-        <v>0</v>
-      </c>
-      <c r="S9" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R9" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="79" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B10" s="49">
         <v>1</v>
@@ -2142,16 +2112,13 @@
       <c r="Q10" s="57">
         <v>0</v>
       </c>
-      <c r="R10" s="57">
-        <v>0</v>
-      </c>
-      <c r="S10" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R10" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" s="52">
         <v>1</v>
@@ -2201,14 +2168,11 @@
       <c r="Q11" s="44">
         <v>0</v>
       </c>
-      <c r="R11" s="44">
-        <v>0</v>
-      </c>
-      <c r="S11" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R11" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>37</v>
       </c>
@@ -2260,16 +2224,13 @@
       <c r="Q12" s="44">
         <v>0</v>
       </c>
-      <c r="R12" s="44">
-        <v>0</v>
-      </c>
-      <c r="S12" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R12" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="79" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B13" s="49">
         <v>1</v>
@@ -2319,16 +2280,13 @@
       <c r="Q13" s="57">
         <v>0</v>
       </c>
-      <c r="R13" s="57">
-        <v>0</v>
-      </c>
-      <c r="S13" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R13" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="79" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B14" s="49">
         <v>1</v>
@@ -2378,14 +2336,11 @@
       <c r="Q14" s="57">
         <v>0</v>
       </c>
-      <c r="R14" s="57">
-        <v>0</v>
-      </c>
-      <c r="S14" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R14" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="48" t="s">
         <v>36</v>
       </c>
@@ -2437,16 +2392,13 @@
       <c r="Q15" s="57">
         <v>0</v>
       </c>
-      <c r="R15" s="57">
-        <v>0</v>
-      </c>
-      <c r="S15" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="R15" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B16" s="49">
         <v>1</v>
@@ -2496,16 +2448,13 @@
       <c r="Q16" s="57">
         <v>0</v>
       </c>
-      <c r="R16" s="57">
-        <v>0</v>
-      </c>
-      <c r="S16" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R16" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" s="55">
         <v>1</v>
@@ -2555,16 +2504,13 @@
       <c r="Q17" s="44">
         <v>0</v>
       </c>
-      <c r="R17" s="44">
-        <v>0</v>
-      </c>
-      <c r="S17" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R17" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="55">
         <v>1</v>
@@ -2614,16 +2560,13 @@
       <c r="Q18" s="44">
         <v>0</v>
       </c>
-      <c r="R18" s="44">
-        <v>0</v>
-      </c>
-      <c r="S18" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R18" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B19" s="55">
         <v>1</v>
@@ -2673,16 +2616,13 @@
       <c r="Q19" s="44">
         <v>0</v>
       </c>
-      <c r="R19" s="44">
-        <v>0</v>
-      </c>
-      <c r="S19" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R19" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B20" s="55">
         <v>1</v>
@@ -2732,16 +2672,13 @@
       <c r="Q20" s="44">
         <v>0</v>
       </c>
-      <c r="R20" s="44">
-        <v>0</v>
-      </c>
-      <c r="S20" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R20" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B21" s="55">
         <v>1</v>
@@ -2791,16 +2728,13 @@
       <c r="Q21" s="44">
         <v>0</v>
       </c>
-      <c r="R21" s="44">
-        <v>0</v>
-      </c>
-      <c r="S21" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B22" s="55">
         <v>2</v>
@@ -2850,16 +2784,13 @@
       <c r="Q22" s="44">
         <v>0</v>
       </c>
-      <c r="R22" s="44">
-        <v>0</v>
-      </c>
-      <c r="S22" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R22" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B23" s="49">
         <v>1</v>
@@ -2909,16 +2840,13 @@
       <c r="Q23" s="57">
         <v>0</v>
       </c>
-      <c r="R23" s="57">
-        <v>0</v>
-      </c>
-      <c r="S23" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R23" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B24" s="49">
         <v>1</v>
@@ -2968,16 +2896,13 @@
       <c r="Q24" s="57">
         <v>0</v>
       </c>
-      <c r="R24" s="57">
-        <v>0</v>
-      </c>
-      <c r="S24" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R24" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="53" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B25" s="52">
         <v>1</v>
@@ -3027,16 +2952,13 @@
       <c r="Q25" s="44">
         <v>0</v>
       </c>
-      <c r="R25" s="44">
-        <v>0</v>
-      </c>
-      <c r="S25" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R25" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B26" s="52">
         <v>1</v>
@@ -3086,16 +3008,13 @@
       <c r="Q26" s="44">
         <v>0</v>
       </c>
-      <c r="R26" s="44">
-        <v>0</v>
-      </c>
-      <c r="S26" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R26" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B27" s="52">
         <v>2</v>
@@ -3145,16 +3064,13 @@
       <c r="Q27" s="44">
         <v>0</v>
       </c>
-      <c r="R27" s="44">
-        <v>0</v>
-      </c>
-      <c r="S27" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R27" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B28" s="49">
         <v>1</v>
@@ -3204,16 +3120,13 @@
       <c r="Q28" s="57">
         <v>0</v>
       </c>
-      <c r="R28" s="57">
-        <v>0</v>
-      </c>
-      <c r="S28" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R28" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B29" s="49">
         <v>1</v>
@@ -3263,16 +3176,13 @@
       <c r="Q29" s="57">
         <v>0</v>
       </c>
-      <c r="R29" s="57">
-        <v>0</v>
-      </c>
-      <c r="S29" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R29" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B30" s="55">
         <v>1</v>
@@ -3322,16 +3232,13 @@
       <c r="Q30" s="44">
         <v>0</v>
       </c>
-      <c r="R30" s="44">
-        <v>0</v>
-      </c>
-      <c r="S30" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R30" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B31" s="55">
         <v>1</v>
@@ -3381,16 +3288,13 @@
       <c r="Q31" s="44">
         <v>0</v>
       </c>
-      <c r="R31" s="44">
-        <v>0</v>
-      </c>
-      <c r="S31" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R31" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B32" s="52">
         <v>1</v>
@@ -3440,16 +3344,13 @@
       <c r="Q32" s="44">
         <v>0</v>
       </c>
-      <c r="R32" s="44">
-        <v>0</v>
-      </c>
-      <c r="S32" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R32" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="79" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B33" s="77">
         <v>1</v>
@@ -3499,16 +3400,13 @@
       <c r="Q33" s="57">
         <v>0</v>
       </c>
-      <c r="R33" s="57">
-        <v>0</v>
-      </c>
-      <c r="S33" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R33" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="79" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B34" s="77">
         <v>1</v>
@@ -3558,16 +3456,13 @@
       <c r="Q34" s="57">
         <v>0</v>
       </c>
-      <c r="R34" s="57">
-        <v>0</v>
-      </c>
-      <c r="S34" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R34" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="78" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B35" s="77">
         <v>1</v>
@@ -3617,16 +3512,13 @@
       <c r="Q35" s="57">
         <v>0</v>
       </c>
-      <c r="R35" s="57">
-        <v>0</v>
-      </c>
-      <c r="S35" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R35" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B36" s="58">
         <v>1</v>
@@ -3676,16 +3568,13 @@
       <c r="Q36" s="57">
         <v>0</v>
       </c>
-      <c r="R36" s="57">
-        <v>0</v>
-      </c>
-      <c r="S36" s="50">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R36" s="50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B37" s="56">
         <v>2</v>
@@ -3735,16 +3624,13 @@
       <c r="Q37" s="44">
         <v>0</v>
       </c>
-      <c r="R37" s="44">
-        <v>0</v>
-      </c>
-      <c r="S37" s="47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R37" s="47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="81" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B38" s="43">
         <v>1</v>
@@ -3797,13 +3683,10 @@
       <c r="R38" s="44">
         <v>0</v>
       </c>
-      <c r="S38" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B39" s="2">
-        <f t="shared" ref="B39:S39" si="0">SUM(B2:B38)</f>
+        <f t="shared" ref="B39:R39" si="0">SUM(B2:B38)</f>
         <v>40</v>
       </c>
       <c r="C39" s="2">
@@ -3867,10 +3750,6 @@
         <v>0</v>
       </c>
       <c r="R39" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3883,14 +3762,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9771D6E0-A82F-43D6-9D85-B15E122031FA}">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="19" width="9.140625" customWidth="1"/>
+    <col min="2" max="18" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
@@ -3921,13 +3800,13 @@
         <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="N1" s="41" t="s">
-        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
         <v>56</v>
@@ -3941,20 +3820,17 @@
       <c r="R1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="41" t="s">
-        <v>60</v>
-      </c>
+      <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B2" s="83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C2" s="12">
         <v>0</v>
@@ -4004,16 +3880,13 @@
       <c r="R2" s="12">
         <v>0</v>
       </c>
-      <c r="S2" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B3" s="83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C3" s="12">
         <v>0</v>
@@ -4063,16 +3936,13 @@
       <c r="R3" s="12">
         <v>0</v>
       </c>
-      <c r="S3" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C4" s="12">
         <v>0</v>
@@ -4122,16 +3992,13 @@
       <c r="R4" s="12">
         <v>0</v>
       </c>
-      <c r="S4" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B5" s="83" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="12">
         <v>0</v>
@@ -4181,16 +4048,13 @@
       <c r="R5" s="12">
         <v>0</v>
       </c>
-      <c r="S5" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="82" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C6" s="18">
         <v>0</v>
@@ -4240,547 +4104,517 @@
       <c r="R6" s="18">
         <v>0</v>
       </c>
-      <c r="S6" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
         <v>41</v>
       </c>
       <c r="B7" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="18">
+        <v>0</v>
+      </c>
+      <c r="D7" s="18">
+        <v>0</v>
+      </c>
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18">
+        <v>0</v>
+      </c>
+      <c r="I7" s="18">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <v>0</v>
+      </c>
+      <c r="L7" s="18">
+        <v>0</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <v>0</v>
+      </c>
+      <c r="O7" s="18">
+        <v>0</v>
+      </c>
+      <c r="P7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>0</v>
+      </c>
+      <c r="R7" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" s="88" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="18">
+        <v>0</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <v>0</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <v>0</v>
+      </c>
+      <c r="O8" s="18">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>0</v>
+      </c>
+      <c r="R8" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="18">
-        <v>0</v>
-      </c>
-      <c r="D7" s="18">
-        <v>0</v>
-      </c>
-      <c r="E7" s="18">
-        <v>0</v>
-      </c>
-      <c r="F7" s="18">
-        <v>0</v>
-      </c>
-      <c r="G7" s="18">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18">
-        <v>0</v>
-      </c>
-      <c r="M7" s="18">
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="18">
-        <v>0</v>
-      </c>
-      <c r="P7" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="18">
-        <v>0</v>
-      </c>
-      <c r="R7" s="18">
-        <v>0</v>
-      </c>
-      <c r="S7" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="88" t="s">
+      <c r="B9" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="18">
+        <v>0</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0</v>
+      </c>
+      <c r="E9" s="18">
+        <v>0</v>
+      </c>
+      <c r="F9" s="18">
+        <v>0</v>
+      </c>
+      <c r="G9" s="18">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>0</v>
+      </c>
+      <c r="O9" s="18">
+        <v>0</v>
+      </c>
+      <c r="P9" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>0</v>
+      </c>
+      <c r="R9" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="18">
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0</v>
+      </c>
+      <c r="E10" s="18">
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0</v>
+      </c>
+      <c r="K10" s="18">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <v>0</v>
+      </c>
+      <c r="M10" s="18">
+        <v>0</v>
+      </c>
+      <c r="N10" s="18">
+        <v>0</v>
+      </c>
+      <c r="O10" s="18">
+        <v>0</v>
+      </c>
+      <c r="P10" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>0</v>
+      </c>
+      <c r="R10" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="18">
-        <v>0</v>
-      </c>
-      <c r="D8" s="18">
-        <v>0</v>
-      </c>
-      <c r="E8" s="18">
-        <v>0</v>
-      </c>
-      <c r="F8" s="18">
-        <v>0</v>
-      </c>
-      <c r="G8" s="18">
-        <v>0</v>
-      </c>
-      <c r="H8" s="18">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0</v>
-      </c>
-      <c r="J8" s="18">
-        <v>0</v>
-      </c>
-      <c r="K8" s="18">
-        <v>0</v>
-      </c>
-      <c r="L8" s="18">
-        <v>0</v>
-      </c>
-      <c r="M8" s="18">
-        <v>0</v>
-      </c>
-      <c r="N8" s="18">
-        <v>0</v>
-      </c>
-      <c r="O8" s="18">
-        <v>0</v>
-      </c>
-      <c r="P8" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="18">
-        <v>0</v>
-      </c>
-      <c r="R8" s="18">
-        <v>0</v>
-      </c>
-      <c r="S8" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
+      <c r="B11" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="18">
+        <v>0</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0</v>
+      </c>
+      <c r="E11" s="18">
+        <v>0</v>
+      </c>
+      <c r="F11" s="18">
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0</v>
+      </c>
+      <c r="K11" s="18">
+        <v>0</v>
+      </c>
+      <c r="L11" s="18">
+        <v>0</v>
+      </c>
+      <c r="M11" s="18">
+        <v>0</v>
+      </c>
+      <c r="N11" s="18">
+        <v>0</v>
+      </c>
+      <c r="O11" s="18">
+        <v>0</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>0</v>
+      </c>
+      <c r="R11" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="18">
-        <v>0</v>
-      </c>
-      <c r="D9" s="18">
-        <v>0</v>
-      </c>
-      <c r="E9" s="18">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18">
-        <v>0</v>
-      </c>
-      <c r="G9" s="18">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <v>0</v>
-      </c>
-      <c r="K9" s="18">
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
-        <v>0</v>
-      </c>
-      <c r="M9" s="18">
-        <v>0</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0</v>
-      </c>
-      <c r="O9" s="18">
-        <v>0</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0</v>
-      </c>
-      <c r="S9" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="18">
-        <v>0</v>
-      </c>
-      <c r="D10" s="18">
-        <v>0</v>
-      </c>
-      <c r="E10" s="18">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <v>0</v>
-      </c>
-      <c r="L10" s="18">
-        <v>0</v>
-      </c>
-      <c r="M10" s="18">
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
-        <v>0</v>
-      </c>
-      <c r="O10" s="18">
-        <v>0</v>
-      </c>
-      <c r="P10" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="18">
-        <v>0</v>
-      </c>
-      <c r="R10" s="18">
-        <v>0</v>
-      </c>
-      <c r="S10" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="B12" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="18">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <v>0</v>
+      </c>
+      <c r="M12" s="18">
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <v>0</v>
+      </c>
+      <c r="O12" s="18">
+        <v>0</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>0</v>
+      </c>
+      <c r="R12" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="18">
+        <v>0</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0</v>
+      </c>
+      <c r="E13" s="18">
+        <v>0</v>
+      </c>
+      <c r="F13" s="18">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18">
+        <v>0</v>
+      </c>
+      <c r="I13" s="18">
+        <v>0</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18">
+        <v>0</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0</v>
+      </c>
+      <c r="M13" s="18">
+        <v>0</v>
+      </c>
+      <c r="N13" s="18">
+        <v>0</v>
+      </c>
+      <c r="O13" s="18">
+        <v>0</v>
+      </c>
+      <c r="P13" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>0</v>
+      </c>
+      <c r="R13" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B11" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11" s="18">
-        <v>0</v>
-      </c>
-      <c r="D11" s="18">
-        <v>0</v>
-      </c>
-      <c r="E11" s="18">
-        <v>0</v>
-      </c>
-      <c r="F11" s="18">
-        <v>0</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18">
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
-        <v>0</v>
-      </c>
-      <c r="L11" s="18">
-        <v>0</v>
-      </c>
-      <c r="M11" s="18">
-        <v>0</v>
-      </c>
-      <c r="N11" s="18">
-        <v>0</v>
-      </c>
-      <c r="O11" s="18">
-        <v>0</v>
-      </c>
-      <c r="P11" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="18">
-        <v>0</v>
-      </c>
-      <c r="R11" s="18">
-        <v>0</v>
-      </c>
-      <c r="S11" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+      <c r="B14" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="18">
+        <v>0</v>
+      </c>
+      <c r="D14" s="18">
+        <v>0</v>
+      </c>
+      <c r="E14" s="18">
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <v>0</v>
+      </c>
+      <c r="I14" s="18">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18">
+        <v>0</v>
+      </c>
+      <c r="L14" s="18">
+        <v>0</v>
+      </c>
+      <c r="M14" s="18">
+        <v>0</v>
+      </c>
+      <c r="N14" s="18">
+        <v>0</v>
+      </c>
+      <c r="O14" s="18">
+        <v>0</v>
+      </c>
+      <c r="P14" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>0</v>
+      </c>
+      <c r="R14" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="18">
-        <v>0</v>
-      </c>
-      <c r="D12" s="18">
-        <v>0</v>
-      </c>
-      <c r="E12" s="18">
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>0</v>
-      </c>
-      <c r="H12" s="18">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <v>0</v>
-      </c>
-      <c r="M12" s="18">
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <v>0</v>
-      </c>
-      <c r="O12" s="18">
-        <v>0</v>
-      </c>
-      <c r="P12" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="18">
-        <v>0</v>
-      </c>
-      <c r="R12" s="18">
-        <v>0</v>
-      </c>
-      <c r="S12" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B13" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" s="18">
-        <v>0</v>
-      </c>
-      <c r="D13" s="18">
-        <v>0</v>
-      </c>
-      <c r="E13" s="18">
-        <v>0</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
-        <v>0</v>
-      </c>
-      <c r="H13" s="18">
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <v>0</v>
-      </c>
-      <c r="K13" s="18">
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <v>0</v>
-      </c>
-      <c r="M13" s="18">
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <v>0</v>
-      </c>
-      <c r="O13" s="18">
-        <v>0</v>
-      </c>
-      <c r="P13" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="18">
-        <v>0</v>
-      </c>
-      <c r="R13" s="18">
-        <v>0</v>
-      </c>
-      <c r="S13" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="B15" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="18">
+        <v>0</v>
+      </c>
+      <c r="D15" s="18">
+        <v>0</v>
+      </c>
+      <c r="E15" s="18">
+        <v>0</v>
+      </c>
+      <c r="F15" s="18">
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <v>0</v>
+      </c>
+      <c r="I15" s="18">
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18">
+        <v>0</v>
+      </c>
+      <c r="L15" s="18">
+        <v>0</v>
+      </c>
+      <c r="M15" s="18">
+        <v>0</v>
+      </c>
+      <c r="N15" s="18">
+        <v>0</v>
+      </c>
+      <c r="O15" s="18">
+        <v>0</v>
+      </c>
+      <c r="P15" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>0</v>
+      </c>
+      <c r="R15" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="18">
-        <v>0</v>
-      </c>
-      <c r="D14" s="18">
-        <v>0</v>
-      </c>
-      <c r="E14" s="18">
-        <v>0</v>
-      </c>
-      <c r="F14" s="18">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18">
-        <v>0</v>
-      </c>
-      <c r="H14" s="18">
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <v>0</v>
-      </c>
-      <c r="K14" s="18">
-        <v>0</v>
-      </c>
-      <c r="L14" s="18">
-        <v>0</v>
-      </c>
-      <c r="M14" s="18">
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <v>0</v>
-      </c>
-      <c r="O14" s="18">
-        <v>0</v>
-      </c>
-      <c r="P14" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>0</v>
-      </c>
-      <c r="R14" s="18">
-        <v>0</v>
-      </c>
-      <c r="S14" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="85" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="18">
-        <v>0</v>
-      </c>
-      <c r="D15" s="18">
-        <v>0</v>
-      </c>
-      <c r="E15" s="18">
-        <v>0</v>
-      </c>
-      <c r="F15" s="18">
-        <v>0</v>
-      </c>
-      <c r="G15" s="18">
-        <v>0</v>
-      </c>
-      <c r="H15" s="18">
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <v>0</v>
-      </c>
-      <c r="K15" s="18">
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <v>0</v>
-      </c>
-      <c r="M15" s="18">
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <v>0</v>
-      </c>
-      <c r="O15" s="18">
-        <v>0</v>
-      </c>
-      <c r="P15" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="18">
-        <v>0</v>
-      </c>
-      <c r="R15" s="18">
-        <v>0</v>
-      </c>
-      <c r="S15" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>110</v>
-      </c>
       <c r="B16" s="85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -4830,16 +4664,13 @@
       <c r="R16" s="18">
         <v>0</v>
       </c>
-      <c r="S16" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -4889,16 +4720,13 @@
       <c r="R17" s="18">
         <v>0</v>
       </c>
-      <c r="S17" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -4948,16 +4776,13 @@
       <c r="R18" s="18">
         <v>0</v>
       </c>
-      <c r="S18" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="89" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" s="19">
         <v>0</v>
@@ -5007,16 +4832,13 @@
       <c r="R19" s="19">
         <v>0</v>
       </c>
-      <c r="S19" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -5066,16 +4888,13 @@
       <c r="R20" s="19">
         <v>0</v>
       </c>
-      <c r="S20" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -5125,16 +4944,13 @@
       <c r="R21" s="19">
         <v>0</v>
       </c>
-      <c r="S21" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -5184,16 +5000,13 @@
       <c r="R22" s="19">
         <v>0</v>
       </c>
-      <c r="S22" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>41</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
@@ -5243,311 +5056,293 @@
       <c r="R23" s="19">
         <v>0</v>
       </c>
-      <c r="S23" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" s="19">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19">
+        <v>0</v>
+      </c>
+      <c r="F24" s="19">
+        <v>0</v>
+      </c>
+      <c r="G24" s="19">
+        <v>0</v>
+      </c>
+      <c r="H24" s="19">
+        <v>0</v>
+      </c>
+      <c r="I24" s="19">
+        <v>0</v>
+      </c>
+      <c r="J24" s="19">
+        <v>0</v>
+      </c>
+      <c r="K24" s="19">
+        <v>0</v>
+      </c>
+      <c r="L24" s="19">
+        <v>0</v>
+      </c>
+      <c r="M24" s="19">
+        <v>0</v>
+      </c>
+      <c r="N24" s="19">
+        <v>0</v>
+      </c>
+      <c r="O24" s="19">
+        <v>0</v>
+      </c>
+      <c r="P24" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>0</v>
+      </c>
+      <c r="R24" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="19">
+        <v>0</v>
+      </c>
+      <c r="D25" s="19">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19">
+        <v>0</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0</v>
+      </c>
+      <c r="H25" s="19">
+        <v>0</v>
+      </c>
+      <c r="I25" s="19">
+        <v>0</v>
+      </c>
+      <c r="J25" s="19">
+        <v>0</v>
+      </c>
+      <c r="K25" s="19">
+        <v>0</v>
+      </c>
+      <c r="L25" s="19">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19">
+        <v>0</v>
+      </c>
+      <c r="N25" s="19">
+        <v>0</v>
+      </c>
+      <c r="O25" s="19">
+        <v>0</v>
+      </c>
+      <c r="P25" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="19">
+        <v>0</v>
+      </c>
+      <c r="R25" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="19">
+        <v>0</v>
+      </c>
+      <c r="D26" s="19">
+        <v>0</v>
+      </c>
+      <c r="E26" s="19">
+        <v>0</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>0</v>
+      </c>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="19">
+        <v>0</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19">
+        <v>0</v>
+      </c>
+      <c r="N26" s="19">
+        <v>0</v>
+      </c>
+      <c r="O26" s="19">
+        <v>0</v>
+      </c>
+      <c r="P26" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="19">
+        <v>0</v>
+      </c>
+      <c r="R26" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="19">
-        <v>0</v>
-      </c>
-      <c r="D24" s="19">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19">
-        <v>0</v>
-      </c>
-      <c r="F24" s="19">
-        <v>0</v>
-      </c>
-      <c r="G24" s="19">
-        <v>0</v>
-      </c>
-      <c r="H24" s="19">
-        <v>0</v>
-      </c>
-      <c r="I24" s="19">
-        <v>0</v>
-      </c>
-      <c r="J24" s="19">
-        <v>0</v>
-      </c>
-      <c r="K24" s="19">
-        <v>0</v>
-      </c>
-      <c r="L24" s="19">
-        <v>0</v>
-      </c>
-      <c r="M24" s="19">
-        <v>0</v>
-      </c>
-      <c r="N24" s="19">
-        <v>0</v>
-      </c>
-      <c r="O24" s="19">
-        <v>0</v>
-      </c>
-      <c r="P24" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="19">
-        <v>0</v>
-      </c>
-      <c r="R24" s="19">
-        <v>0</v>
-      </c>
-      <c r="S24" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="86" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="19">
-        <v>0</v>
-      </c>
-      <c r="D25" s="19">
-        <v>0</v>
-      </c>
-      <c r="E25" s="19">
-        <v>0</v>
-      </c>
-      <c r="F25" s="19">
-        <v>0</v>
-      </c>
-      <c r="G25" s="19">
-        <v>0</v>
-      </c>
-      <c r="H25" s="19">
-        <v>0</v>
-      </c>
-      <c r="I25" s="19">
-        <v>0</v>
-      </c>
-      <c r="J25" s="19">
-        <v>0</v>
-      </c>
-      <c r="K25" s="19">
-        <v>0</v>
-      </c>
-      <c r="L25" s="19">
-        <v>0</v>
-      </c>
-      <c r="M25" s="19">
-        <v>0</v>
-      </c>
-      <c r="N25" s="19">
-        <v>0</v>
-      </c>
-      <c r="O25" s="19">
-        <v>0</v>
-      </c>
-      <c r="P25" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="19">
-        <v>0</v>
-      </c>
-      <c r="R25" s="19">
-        <v>0</v>
-      </c>
-      <c r="S25" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="B27" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="19">
+        <v>0</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0</v>
+      </c>
+      <c r="E27" s="19">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>0</v>
+      </c>
+      <c r="I27" s="19">
+        <v>0</v>
+      </c>
+      <c r="J27" s="19">
+        <v>0</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19">
+        <v>0</v>
+      </c>
+      <c r="N27" s="19">
+        <v>0</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19">
+        <v>0</v>
+      </c>
+      <c r="R27" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="19">
+        <v>0</v>
+      </c>
+      <c r="D28" s="19">
+        <v>0</v>
+      </c>
+      <c r="E28" s="19">
+        <v>0</v>
+      </c>
+      <c r="F28" s="19">
+        <v>0</v>
+      </c>
+      <c r="G28" s="19">
+        <v>0</v>
+      </c>
+      <c r="H28" s="19">
+        <v>0</v>
+      </c>
+      <c r="I28" s="19">
+        <v>0</v>
+      </c>
+      <c r="J28" s="19">
+        <v>0</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19">
+        <v>0</v>
+      </c>
+      <c r="N28" s="19">
+        <v>0</v>
+      </c>
+      <c r="O28" s="19">
+        <v>0</v>
+      </c>
+      <c r="P28" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="19">
+        <v>0</v>
+      </c>
+      <c r="R28" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="19">
-        <v>0</v>
-      </c>
-      <c r="D26" s="19">
-        <v>0</v>
-      </c>
-      <c r="E26" s="19">
-        <v>0</v>
-      </c>
-      <c r="F26" s="19">
-        <v>0</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0</v>
-      </c>
-      <c r="H26" s="19">
-        <v>0</v>
-      </c>
-      <c r="I26" s="19">
-        <v>0</v>
-      </c>
-      <c r="J26" s="19">
-        <v>0</v>
-      </c>
-      <c r="K26" s="19">
-        <v>0</v>
-      </c>
-      <c r="L26" s="19">
-        <v>0</v>
-      </c>
-      <c r="M26" s="19">
-        <v>0</v>
-      </c>
-      <c r="N26" s="19">
-        <v>0</v>
-      </c>
-      <c r="O26" s="19">
-        <v>0</v>
-      </c>
-      <c r="P26" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="19">
-        <v>0</v>
-      </c>
-      <c r="R26" s="19">
-        <v>0</v>
-      </c>
-      <c r="S26" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="B27" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="C27" s="19">
-        <v>0</v>
-      </c>
-      <c r="D27" s="19">
-        <v>0</v>
-      </c>
-      <c r="E27" s="19">
-        <v>0</v>
-      </c>
-      <c r="F27" s="19">
-        <v>0</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19">
-        <v>0</v>
-      </c>
-      <c r="I27" s="19">
-        <v>0</v>
-      </c>
-      <c r="J27" s="19">
-        <v>0</v>
-      </c>
-      <c r="K27" s="19">
-        <v>0</v>
-      </c>
-      <c r="L27" s="19">
-        <v>0</v>
-      </c>
-      <c r="M27" s="19">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19">
-        <v>0</v>
-      </c>
-      <c r="O27" s="19">
-        <v>0</v>
-      </c>
-      <c r="P27" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="19">
-        <v>0</v>
-      </c>
-      <c r="R27" s="19">
-        <v>0</v>
-      </c>
-      <c r="S27" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" s="19">
-        <v>0</v>
-      </c>
-      <c r="D28" s="19">
-        <v>0</v>
-      </c>
-      <c r="E28" s="19">
-        <v>0</v>
-      </c>
-      <c r="F28" s="19">
-        <v>0</v>
-      </c>
-      <c r="G28" s="19">
-        <v>0</v>
-      </c>
-      <c r="H28" s="19">
-        <v>0</v>
-      </c>
-      <c r="I28" s="19">
-        <v>0</v>
-      </c>
-      <c r="J28" s="19">
-        <v>0</v>
-      </c>
-      <c r="K28" s="19">
-        <v>0</v>
-      </c>
-      <c r="L28" s="19">
-        <v>0</v>
-      </c>
-      <c r="M28" s="19">
-        <v>0</v>
-      </c>
-      <c r="N28" s="19">
-        <v>0</v>
-      </c>
-      <c r="O28" s="19">
-        <v>0</v>
-      </c>
-      <c r="P28" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="19">
-        <v>0</v>
-      </c>
-      <c r="R28" s="19">
-        <v>0</v>
-      </c>
-      <c r="S28" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>115</v>
-      </c>
       <c r="B29" s="86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -5565,14 +5360,13 @@
       <c r="P29" s="19"/>
       <c r="Q29" s="19"/>
       <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
@@ -5622,11 +5416,8 @@
       <c r="R30" s="19">
         <v>0</v>
       </c>
-      <c r="S30" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B31" s="87">
         <v>40</v>
       </c>
@@ -5643,7 +5434,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="2">
-        <f t="shared" ref="F31:R31" si="0">SUM(F2:F30)</f>
+        <f t="shared" ref="F31:Q31" si="0">SUM(F2:F30)</f>
         <v>0</v>
       </c>
       <c r="G31" s="2">
@@ -5691,11 +5482,7 @@
         <v>0</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="2">
-        <f>SUM(S2:S30)</f>
+        <f>SUM(R2:R30)</f>
         <v>0</v>
       </c>
     </row>
@@ -5706,19 +5493,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X984"/>
+  <dimension ref="A1:W984"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="7.140625" customWidth="1"/>
-    <col min="5" max="18" width="6.85546875" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" customWidth="1"/>
-    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="5" max="17" width="6.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.5703125" customWidth="1"/>
+    <col min="19" max="23" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="121.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="121.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
@@ -5749,13 +5536,13 @@
         <v>52</v>
       </c>
       <c r="L1" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="N1" s="41" t="s">
-        <v>54</v>
       </c>
       <c r="O1" s="41" t="s">
         <v>56</v>
@@ -5769,15 +5556,12 @@
       <c r="R1" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="S1" s="41" t="s">
-        <v>60</v>
-      </c>
+      <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -5798,11 +5582,10 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
       <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-    </row>
-    <row r="3" spans="1:24" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="90" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B3" s="61">
         <v>1</v>
@@ -5855,11 +5638,8 @@
       <c r="R3" s="62">
         <v>0</v>
       </c>
-      <c r="S3" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:23" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="60" t="s">
         <v>1</v>
       </c>
@@ -5914,11 +5694,8 @@
       <c r="R4" s="62">
         <v>0</v>
       </c>
-      <c r="S4" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="60" t="s">
         <v>2</v>
       </c>
@@ -5973,11 +5750,8 @@
       <c r="R5" s="62">
         <v>0</v>
       </c>
-      <c r="S5" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="60" t="s">
         <v>3</v>
       </c>
@@ -6032,11 +5806,8 @@
       <c r="R6" s="62">
         <v>0</v>
       </c>
-      <c r="S6" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="60" t="s">
         <v>4</v>
       </c>
@@ -6091,11 +5862,8 @@
       <c r="R7" s="62">
         <v>0</v>
       </c>
-      <c r="S7" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
@@ -6116,11 +5884,10 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="91" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B9" s="68">
         <v>3</v>
@@ -6173,13 +5940,10 @@
       <c r="R9" s="69">
         <v>0</v>
       </c>
-      <c r="S9" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B10" s="68">
         <v>2</v>
@@ -6232,13 +5996,10 @@
       <c r="R10" s="69">
         <v>0</v>
       </c>
-      <c r="S10" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="91" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B11" s="68">
         <v>2</v>
@@ -6291,13 +6052,10 @@
       <c r="R11" s="69">
         <v>0</v>
       </c>
-      <c r="S11" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="91" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12" s="68">
         <v>1</v>
@@ -6350,13 +6108,10 @@
       <c r="R12" s="69">
         <v>0</v>
       </c>
-      <c r="S12" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="91" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B13" s="68">
         <v>1</v>
@@ -6409,13 +6164,10 @@
       <c r="R13" s="69">
         <v>0</v>
       </c>
-      <c r="S13" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="91" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14" s="68">
         <v>4</v>
@@ -6468,13 +6220,10 @@
       <c r="R14" s="69">
         <v>0</v>
       </c>
-      <c r="S14" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="91" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B15" s="68">
         <v>1</v>
@@ -6527,13 +6276,10 @@
       <c r="R15" s="69">
         <v>0</v>
       </c>
-      <c r="S15" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="91" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16" s="68">
         <v>1</v>
@@ -6586,13 +6332,10 @@
       <c r="R16" s="69">
         <v>0</v>
       </c>
-      <c r="S16" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="91" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B17" s="68">
         <v>4</v>
@@ -6645,11 +6388,8 @@
       <c r="R17" s="69">
         <v>0</v>
       </c>
-      <c r="S17" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
         <v>42</v>
       </c>
@@ -6704,11 +6444,8 @@
       <c r="R18" s="69">
         <v>0</v>
       </c>
-      <c r="S18" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
@@ -6729,9 +6466,8 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
         <v>43</v>
       </c>
@@ -6786,13 +6522,10 @@
       <c r="R20" s="71">
         <v>0</v>
       </c>
-      <c r="S20" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="92" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B21" s="70">
         <v>1</v>
@@ -6845,13 +6578,10 @@
       <c r="R21" s="71">
         <v>0</v>
       </c>
-      <c r="S21" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B22" s="70">
         <v>1</v>
@@ -6904,13 +6634,10 @@
       <c r="R22" s="71">
         <v>0</v>
       </c>
-      <c r="S22" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B23" s="70">
         <v>1</v>
@@ -6963,13 +6690,10 @@
       <c r="R23" s="71">
         <v>0</v>
       </c>
-      <c r="S23" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B24" s="70">
         <v>1</v>
@@ -7022,13 +6746,10 @@
       <c r="R24" s="71">
         <v>0</v>
       </c>
-      <c r="S24" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B25" s="70">
         <v>1</v>
@@ -7081,13 +6802,10 @@
       <c r="R25" s="71">
         <v>0</v>
       </c>
-      <c r="S25" s="71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="3"/>
@@ -7106,11 +6824,10 @@
       <c r="P26" s="3"/>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B27" s="72">
         <v>2</v>
@@ -7163,13 +6880,10 @@
       <c r="R27" s="73">
         <v>0</v>
       </c>
-      <c r="S27" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B28" s="72">
         <v>2</v>
@@ -7222,13 +6936,10 @@
       <c r="R28" s="73">
         <v>0</v>
       </c>
-      <c r="S28" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B29" s="72">
         <v>1</v>
@@ -7281,13 +6992,10 @@
       <c r="R29" s="73">
         <v>0</v>
       </c>
-      <c r="S29" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B30" s="72">
         <v>1</v>
@@ -7340,13 +7048,10 @@
       <c r="R30" s="73">
         <v>0</v>
       </c>
-      <c r="S30" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B31" s="72">
         <v>1</v>
@@ -7399,11 +7104,8 @@
       <c r="R31" s="73">
         <v>0</v>
       </c>
-      <c r="S31" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="65" t="s">
         <v>11</v>
       </c>
@@ -7458,11 +7160,8 @@
       <c r="R32" s="73">
         <v>0</v>
       </c>
-      <c r="S32" s="73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="76" t="s">
         <v>12</v>
       </c>
@@ -7483,11 +7182,10 @@
       <c r="P33" s="3"/>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="95" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B34" s="66">
         <v>1</v>
@@ -7540,18 +7238,15 @@
       <c r="R34" s="67">
         <v>0</v>
       </c>
-      <c r="S34" s="67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="74"/>
       <c r="B35" s="75">
         <f>SUM(B3:B34)</f>
         <v>40</v>
       </c>
       <c r="C35" s="75">
-        <f t="shared" ref="C35:S35" si="0">SUM(C3:C34)</f>
+        <f t="shared" ref="C35:R35" si="0">SUM(C3:C34)</f>
         <v>0</v>
       </c>
       <c r="D35" s="75">
@@ -7614,24 +7309,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S35" s="75">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="36" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8857,10 +8548,10 @@
     </row>
     <row r="6" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="30">
         <v>30</v>
@@ -8910,10 +8601,10 @@
     </row>
     <row r="7" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="30">
         <v>30</v>
@@ -8963,10 +8654,10 @@
     </row>
     <row r="8" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="30">
         <v>30</v>
@@ -9016,10 +8707,10 @@
     </row>
     <row r="9" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" s="30">
         <v>30</v>
@@ -9069,10 +8760,10 @@
     </row>
     <row r="10" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="30">
         <v>30</v>
@@ -9122,10 +8813,10 @@
     </row>
     <row r="11" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C11" s="30">
         <v>30</v>
@@ -9175,10 +8866,10 @@
     </row>
     <row r="12" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="30">
         <v>30</v>
@@ -9228,10 +8919,10 @@
     </row>
     <row r="13" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" s="30">
         <v>30</v>
@@ -9281,10 +8972,10 @@
     </row>
     <row r="14" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C14" s="30">
         <v>30</v>
@@ -9334,10 +9025,10 @@
     </row>
     <row r="15" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C15" s="30">
         <v>30</v>
@@ -9387,10 +9078,10 @@
     </row>
     <row r="16" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="30">
         <v>30</v>
@@ -9440,10 +9131,10 @@
     </row>
     <row r="17" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="30">
         <v>30</v>

--- a/javitolap.xlsx
+++ b/javitolap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Peter\Desktop\2026_alapvizsga\2026_alapvizsga_eles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3087B41-0D5C-4708-8C65-AF370B5845F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A62F005-B652-4D05-8E1E-DABAC5FC0707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Webprogramozas" sheetId="5" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="147">
   <si>
     <t>A megoldás mentése, eszközök elhelyezése</t>
   </si>
@@ -145,18 +145,6 @@
   </si>
   <si>
     <t>0%-39%</t>
-  </si>
-  <si>
-    <t>40%-59%</t>
-  </si>
-  <si>
-    <t>60%-74%</t>
-  </si>
-  <si>
-    <t>75%-89%</t>
-  </si>
-  <si>
-    <t>90%-100%</t>
   </si>
   <si>
     <t>Bootstrap js állomány beimportálása</t>
@@ -652,6 +640,18 @@
   </si>
   <si>
     <t>5.</t>
+  </si>
+  <si>
+    <t>40%-54%</t>
+  </si>
+  <si>
+    <t>55%-69%</t>
+  </si>
+  <si>
+    <t>70%-84%</t>
+  </si>
+  <si>
+    <t>85%-100%</t>
   </si>
 </sst>
 </file>
@@ -1560,52 +1560,52 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="H1" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="I1" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="J1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="K1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="L1" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="O1" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="P1" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="41" t="s">
+      <c r="R1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="41" t="s">
-        <v>59</v>
       </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1614,114 +1614,114 @@
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B2" s="43">
         <v>1</v>
       </c>
       <c r="C2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="46">
         <v>1</v>
       </c>
       <c r="C3" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -1732,52 +1732,52 @@
         <v>1</v>
       </c>
       <c r="C4" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -1788,52 +1788,52 @@
         <v>1</v>
       </c>
       <c r="C5" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -1844,108 +1844,108 @@
         <v>1</v>
       </c>
       <c r="C6" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="79" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B7" s="49">
         <v>1</v>
       </c>
       <c r="C7" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
@@ -1956,52 +1956,52 @@
         <v>1</v>
       </c>
       <c r="C8" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
@@ -2012,225 +2012,225 @@
         <v>1</v>
       </c>
       <c r="C9" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="79" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B10" s="49">
         <v>1</v>
       </c>
       <c r="C10" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="53" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B11" s="52">
         <v>1</v>
       </c>
       <c r="C11" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="44">
         <v>0</v>
       </c>
       <c r="O11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B12" s="52">
         <v>1</v>
       </c>
       <c r="C12" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="79" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B13" s="49">
         <v>1</v>
@@ -2239,34 +2239,34 @@
         <v>0</v>
       </c>
       <c r="D13" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" s="57">
         <v>0</v>
@@ -2275,163 +2275,163 @@
         <v>0</v>
       </c>
       <c r="P13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="79" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B14" s="49">
         <v>1</v>
       </c>
       <c r="C14" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="48" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B15" s="49">
         <v>1</v>
       </c>
       <c r="C15" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="79" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B16" s="49">
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="50">
         <v>0</v>
       </c>
       <c r="E16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="57">
         <v>0</v>
@@ -2440,27 +2440,27 @@
         <v>0</v>
       </c>
       <c r="O16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B17" s="55">
         <v>1</v>
       </c>
       <c r="C17" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="47">
         <v>0</v>
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="44">
         <v>0</v>
@@ -2481,13 +2481,13 @@
         <v>0</v>
       </c>
       <c r="J17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="44">
         <v>0</v>
@@ -2499,24 +2499,24 @@
         <v>0</v>
       </c>
       <c r="P17" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="44">
         <v>0</v>
       </c>
       <c r="R17" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B18" s="55">
         <v>1</v>
       </c>
       <c r="C18" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="47">
         <v>0</v>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" s="44">
         <v>0</v>
@@ -2537,13 +2537,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="44">
         <v>0</v>
@@ -2555,24 +2555,24 @@
         <v>0</v>
       </c>
       <c r="P18" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" s="44">
         <v>0</v>
       </c>
       <c r="R18" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B19" s="55">
         <v>1</v>
       </c>
       <c r="C19" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="47">
         <v>0</v>
@@ -2584,22 +2584,22 @@
         <v>0</v>
       </c>
       <c r="G19" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="44">
         <v>0</v>
       </c>
       <c r="J19" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="44">
         <v>0</v>
@@ -2617,12 +2617,12 @@
         <v>0</v>
       </c>
       <c r="R19" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="54" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B20" s="55">
         <v>1</v>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" s="44">
         <v>0</v>
@@ -2652,10 +2652,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="44">
         <v>0</v>
@@ -2673,12 +2673,12 @@
         <v>0</v>
       </c>
       <c r="R20" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B21" s="55">
         <v>1</v>
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="44">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="K21" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="44">
         <v>0</v>
@@ -2734,7 +2734,7 @@
     </row>
     <row r="22" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="54" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B22" s="55">
         <v>2</v>
@@ -2790,105 +2790,105 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="79" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B23" s="49">
         <v>1</v>
       </c>
       <c r="C23" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="79" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B24" s="49">
         <v>1</v>
       </c>
       <c r="C24" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="57">
         <v>0</v>
@@ -2897,12 +2897,12 @@
         <v>0</v>
       </c>
       <c r="R24" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="53" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B25" s="52">
         <v>1</v>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="44">
         <v>0</v>
@@ -2920,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="G25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="44">
         <v>0</v>
@@ -2929,25 +2929,25 @@
         <v>0</v>
       </c>
       <c r="J25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="44">
         <v>0</v>
       </c>
       <c r="P25" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="44">
         <v>0</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B26" s="52">
         <v>1</v>
@@ -2976,7 +2976,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="44">
         <v>0</v>
@@ -2988,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="K26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" s="44">
         <v>0</v>
@@ -3003,63 +3003,63 @@
         <v>0</v>
       </c>
       <c r="P26" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="44">
         <v>0</v>
       </c>
       <c r="R26" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="53" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B27" s="52">
         <v>2</v>
       </c>
       <c r="C27" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="44">
         <v>0</v>
       </c>
       <c r="J27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="44">
         <v>0</v>
       </c>
       <c r="P27" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="44">
         <v>0</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="28" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="79" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B28" s="49">
         <v>1</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="K28" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="57">
         <v>0</v>
@@ -3121,12 +3121,12 @@
         <v>0</v>
       </c>
       <c r="R28" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="79" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B29" s="49">
         <v>1</v>
@@ -3156,10 +3156,10 @@
         <v>0</v>
       </c>
       <c r="K29" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="57">
         <v>0</v>
@@ -3177,68 +3177,68 @@
         <v>0</v>
       </c>
       <c r="R29" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B30" s="55">
         <v>1</v>
       </c>
       <c r="C30" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" s="44">
         <v>0</v>
       </c>
       <c r="J30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="44">
         <v>0</v>
       </c>
       <c r="N30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="44">
         <v>0</v>
       </c>
       <c r="P30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:18" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="54" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B31" s="55">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" s="44">
         <v>0</v>
@@ -3271,13 +3271,13 @@
         <v>0</v>
       </c>
       <c r="L31" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="44">
         <v>0</v>
       </c>
       <c r="N31" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="44">
         <v>0</v>
@@ -3289,12 +3289,12 @@
         <v>0</v>
       </c>
       <c r="R31" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="51" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B32" s="52">
         <v>1</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="44">
         <v>0</v>
@@ -3321,19 +3321,19 @@
         <v>0</v>
       </c>
       <c r="J32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" s="44">
         <v>0</v>
       </c>
       <c r="L32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="44">
         <v>0</v>
       </c>
       <c r="N32" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="44">
         <v>0</v>
@@ -3345,12 +3345,12 @@
         <v>0</v>
       </c>
       <c r="R32" s="47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="79" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B33" s="77">
         <v>1</v>
@@ -3368,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="57">
         <v>0</v>
@@ -3380,10 +3380,10 @@
         <v>0</v>
       </c>
       <c r="K33" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="57">
         <v>0</v>
@@ -3395,10 +3395,10 @@
         <v>0</v>
       </c>
       <c r="P33" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="50">
         <v>0</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="79" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B34" s="77">
         <v>1</v>
       </c>
       <c r="C34" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="50">
         <v>0</v>
@@ -3424,28 +3424,28 @@
         <v>0</v>
       </c>
       <c r="G34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="57">
         <v>0</v>
       </c>
       <c r="I34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="57">
         <v>0</v>
       </c>
       <c r="N34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" s="57">
         <v>0</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="50">
         <v>0</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="78" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B35" s="77">
         <v>1</v>
       </c>
       <c r="C35" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="57">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" s="57">
         <v>0</v>
@@ -3489,16 +3489,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="57">
         <v>0</v>
@@ -3507,18 +3507,18 @@
         <v>0</v>
       </c>
       <c r="P35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="80" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B36" s="58">
         <v>1</v>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
       <c r="G36" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="57">
         <v>0</v>
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="K36" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="57">
         <v>0</v>
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" s="50">
         <v>0</v>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="53" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B37" s="56">
         <v>2</v>
@@ -3592,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="44">
         <v>0</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="81" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B38" s="43">
         <v>1</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="44">
         <v>0</v>
@@ -3691,67 +3691,67 @@
       </c>
       <c r="C39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L39" s="2">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(L2:L38)</f>
+        <v>33</v>
       </c>
       <c r="M39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="P39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="R39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3773,52 +3773,52 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="H1" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="I1" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="J1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="K1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="L1" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="O1" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="P1" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="41" t="s">
+      <c r="R1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="41" t="s">
-        <v>59</v>
       </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -3827,361 +3827,361 @@
     </row>
     <row r="2" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B2" s="83" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B3" s="83" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R3" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B4" s="83" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C4" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B5" s="83" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C5" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="82" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="59" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="85" t="s">
-        <v>101</v>
+        <v>37</v>
+      </c>
+      <c r="B7" s="85">
+        <v>2</v>
       </c>
       <c r="C7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="88" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="85" t="s">
-        <v>101</v>
+        <v>98</v>
+      </c>
+      <c r="B8" s="85">
+        <v>1</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
       </c>
       <c r="D8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="18">
         <v>0</v>
@@ -4190,54 +4190,54 @@
         <v>0</v>
       </c>
       <c r="J8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="18">
         <v>0</v>
       </c>
       <c r="P8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B9" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C9" s="18">
         <v>0</v>
       </c>
       <c r="D9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="18">
         <v>0</v>
@@ -4246,54 +4246,54 @@
         <v>0</v>
       </c>
       <c r="J9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="18">
         <v>0</v>
       </c>
       <c r="P9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>100</v>
+        <v>113</v>
+      </c>
+      <c r="B10" s="85">
+        <v>1</v>
       </c>
       <c r="C10" s="18">
         <v>0</v>
       </c>
       <c r="D10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="18">
         <v>0</v>
       </c>
       <c r="G10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="18">
         <v>0</v>
@@ -4302,54 +4302,54 @@
         <v>0</v>
       </c>
       <c r="J10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="18">
         <v>0</v>
       </c>
       <c r="P10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B11" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C11" s="18">
         <v>0</v>
       </c>
       <c r="D11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" s="18">
         <v>0</v>
@@ -4358,45 +4358,45 @@
         <v>0</v>
       </c>
       <c r="J11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="18">
         <v>0</v>
       </c>
       <c r="P11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" s="18">
         <v>0</v>
       </c>
       <c r="R11" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B12" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C12" s="18">
         <v>0</v>
       </c>
       <c r="D12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="18">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="18">
         <v>0</v>
@@ -4414,39 +4414,39 @@
         <v>0</v>
       </c>
       <c r="J12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="18">
         <v>0</v>
       </c>
       <c r="P12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="18">
         <v>0</v>
       </c>
       <c r="R12" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B13" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="18">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="18">
         <v>0</v>
@@ -4488,21 +4488,21 @@
         <v>0</v>
       </c>
       <c r="P13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="18">
         <v>0</v>
       </c>
       <c r="R13" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B14" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="18">
         <v>0</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B15" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -4588,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="18">
         <v>0</v>
@@ -4611,10 +4611,10 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B16" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" s="18">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="18">
         <v>0</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" s="18">
         <v>0</v>
@@ -4697,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="18">
         <v>0</v>
@@ -4723,10 +4723,10 @@
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B18" s="85" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -4756,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="L18" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="18">
         <v>0</v>
@@ -4779,58 +4779,58 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="89" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -4838,63 +4838,63 @@
         <v>14</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R20" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C21" s="19">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="19">
         <v>0</v>
@@ -4930,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="19">
         <v>0</v>
@@ -4947,10 +4947,10 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C22" s="19">
         <v>0</v>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="19">
         <v>0</v>
@@ -4986,7 +4986,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="19">
         <v>0</v>
@@ -5003,16 +5003,16 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" s="19">
         <v>0</v>
       </c>
       <c r="D23" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="19">
         <v>0</v>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="G23" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" s="19">
         <v>0</v>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="19">
         <v>0</v>
@@ -5042,7 +5042,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="19">
         <v>0</v>
@@ -5059,10 +5059,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C24" s="19">
         <v>0</v>
@@ -5115,10 +5115,10 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C25" s="19">
         <v>0</v>
@@ -5171,10 +5171,10 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C26" s="19">
         <v>0</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B27" s="86" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C27" s="19">
         <v>0</v>
@@ -5283,10 +5283,10 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B28" s="86" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="19">
         <v>0</v>
@@ -5339,34 +5339,66 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="19"/>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
+        <v>97</v>
+      </c>
+      <c r="C29" s="19">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19">
+        <v>0</v>
+      </c>
+      <c r="E29" s="19">
+        <v>0</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0</v>
+      </c>
+      <c r="H29" s="19">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>0</v>
+      </c>
+      <c r="J29" s="19">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
+        <v>0</v>
+      </c>
+      <c r="L29" s="19">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19">
+        <v>0</v>
+      </c>
+      <c r="N29" s="19">
+        <v>0</v>
+      </c>
+      <c r="O29" s="19">
+        <v>0</v>
+      </c>
+      <c r="P29" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="19">
+        <v>0</v>
+      </c>
+      <c r="R29" s="19">
+        <v>0</v>
+      </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
@@ -5423,67 +5455,67 @@
       </c>
       <c r="C31" s="2">
         <f>SUM(C2:C30)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2">
         <f>SUM(D2:D30)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E31" s="2">
         <f>SUM(E2:E30)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" ref="F31:Q31" si="0">SUM(F2:F30)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q31" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R31" s="2">
         <f>SUM(R2:R30)</f>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -5509,52 +5541,52 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="H1" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="I1" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="J1" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="K1" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="L1" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" s="41" t="s">
+      <c r="N1" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="O1" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="P1" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q1" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="N1" s="41" t="s">
+      <c r="R1" s="41" t="s">
         <v>55</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="R1" s="41" t="s">
-        <v>59</v>
       </c>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -5585,7 +5617,7 @@
     </row>
     <row r="3" spans="1:23" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="90" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B3" s="61">
         <v>1</v>
@@ -5887,7 +5919,7 @@
     </row>
     <row r="9" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="91" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B9" s="68">
         <v>3</v>
@@ -5943,7 +5975,7 @@
     </row>
     <row r="10" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="91" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B10" s="68">
         <v>2</v>
@@ -5999,7 +6031,7 @@
     </row>
     <row r="11" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="91" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B11" s="68">
         <v>2</v>
@@ -6055,7 +6087,7 @@
     </row>
     <row r="12" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="91" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B12" s="68">
         <v>1</v>
@@ -6111,7 +6143,7 @@
     </row>
     <row r="13" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="91" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B13" s="68">
         <v>1</v>
@@ -6167,7 +6199,7 @@
     </row>
     <row r="14" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="91" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B14" s="68">
         <v>4</v>
@@ -6223,7 +6255,7 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="91" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B15" s="68">
         <v>1</v>
@@ -6279,7 +6311,7 @@
     </row>
     <row r="16" spans="1:23" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="91" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B16" s="68">
         <v>1</v>
@@ -6335,7 +6367,7 @@
     </row>
     <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="91" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B17" s="68">
         <v>4</v>
@@ -6391,7 +6423,7 @@
     </row>
     <row r="18" spans="1:18" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="63" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="68">
         <v>1</v>
@@ -6469,7 +6501,7 @@
     </row>
     <row r="20" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="64" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" s="70">
         <v>1</v>
@@ -6525,7 +6557,7 @@
     </row>
     <row r="21" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="92" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B21" s="70">
         <v>1</v>
@@ -6581,7 +6613,7 @@
     </row>
     <row r="22" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="93" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B22" s="70">
         <v>1</v>
@@ -6637,7 +6669,7 @@
     </row>
     <row r="23" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="93" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B23" s="70">
         <v>1</v>
@@ -6693,7 +6725,7 @@
     </row>
     <row r="24" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="93" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B24" s="70">
         <v>1</v>
@@ -6749,7 +6781,7 @@
     </row>
     <row r="25" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="93" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B25" s="70">
         <v>1</v>
@@ -6805,7 +6837,7 @@
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="3"/>
@@ -6827,7 +6859,7 @@
     </row>
     <row r="27" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="94" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B27" s="72">
         <v>2</v>
@@ -6883,7 +6915,7 @@
     </row>
     <row r="28" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="94" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B28" s="72">
         <v>2</v>
@@ -6939,7 +6971,7 @@
     </row>
     <row r="29" spans="1:18" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="94" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B29" s="72">
         <v>1</v>
@@ -6995,7 +7027,7 @@
     </row>
     <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="94" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B30" s="72">
         <v>1</v>
@@ -7051,7 +7083,7 @@
     </row>
     <row r="31" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="94" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B31" s="72">
         <v>1</v>
@@ -7185,7 +7217,7 @@
     </row>
     <row r="34" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="95" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B34" s="66">
         <v>1</v>
@@ -8339,38 +8371,38 @@
         <v>26</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C2" s="30">
         <v>30</v>
       </c>
       <c r="D2" s="30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E2" s="31">
         <f t="shared" ref="E2:E17" si="0">D2/C2</f>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F2" s="32">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2" s="30">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H2" s="33">
         <v>0</v>
       </c>
       <c r="I2" s="30">
         <f t="shared" ref="I2:I17" si="1">SUM(F2:H2)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J2" s="34">
         <f t="shared" ref="J2:J17" si="2">I2/120</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K2" s="35">
         <f>E2*0.1+J2*0.9</f>
-        <v>0</v>
+        <v>0.33666666666666667</v>
       </c>
       <c r="L2" s="36"/>
       <c r="M2" s="37"/>
@@ -8392,38 +8424,38 @@
         <v>27</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" s="30">
         <v>30</v>
       </c>
       <c r="D3" s="30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E3" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F3" s="32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3" s="30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H3" s="33">
         <v>0</v>
       </c>
       <c r="I3" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J3" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K3" s="35">
         <f t="shared" ref="K3:K16" si="3">E3*0.1+J3*0.9</f>
-        <v>0</v>
+        <v>0.38166666666666665</v>
       </c>
       <c r="L3" s="36"/>
       <c r="M3" s="37"/>
@@ -8445,38 +8477,38 @@
         <v>28</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C4" s="30">
         <v>30</v>
       </c>
       <c r="D4" s="30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E4" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F4" s="32">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4" s="30">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H4" s="33">
         <v>0</v>
       </c>
       <c r="I4" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J4" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="K4" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.35833333333333328</v>
       </c>
       <c r="L4" s="36"/>
       <c r="M4" s="37"/>
@@ -8498,38 +8530,38 @@
         <v>29</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C5" s="30">
         <v>30</v>
       </c>
       <c r="D5" s="30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E5" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="32">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5" s="30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H5" s="33">
         <v>0</v>
       </c>
       <c r="I5" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J5" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.30833333333333335</v>
       </c>
       <c r="K5" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.33750000000000002</v>
       </c>
       <c r="L5" s="36"/>
       <c r="M5" s="37"/>
@@ -8548,41 +8580,41 @@
     </row>
     <row r="6" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="28" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C6" s="30">
         <v>30</v>
       </c>
       <c r="D6" s="30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E6" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F6" s="32">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G6" s="30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H6" s="33">
         <v>0</v>
       </c>
       <c r="I6" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J6" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.53666666666666663</v>
       </c>
       <c r="L6" s="36"/>
       <c r="M6" s="37"/>
@@ -8601,41 +8633,41 @@
     </row>
     <row r="7" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C7" s="30">
         <v>30</v>
       </c>
       <c r="D7" s="30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E7" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F7" s="32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7" s="30">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H7" s="33">
         <v>0</v>
       </c>
       <c r="I7" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J7" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="K7" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.34916666666666668</v>
       </c>
       <c r="L7" s="36"/>
       <c r="M7" s="37"/>
@@ -8654,41 +8686,41 @@
     </row>
     <row r="8" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C8" s="30">
         <v>30</v>
       </c>
       <c r="D8" s="30">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E8" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="32">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G8" s="30">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H8" s="33">
         <v>0</v>
       </c>
       <c r="I8" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="K8" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.28750000000000003</v>
       </c>
       <c r="L8" s="36"/>
       <c r="M8" s="37"/>
@@ -8707,41 +8739,41 @@
     </row>
     <row r="9" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C9" s="30">
         <v>30</v>
       </c>
       <c r="D9" s="30">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E9" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F9" s="32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G9" s="30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H9" s="33">
         <v>0</v>
       </c>
       <c r="I9" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J9" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.38333333333333336</v>
       </c>
       <c r="K9" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.42500000000000004</v>
       </c>
       <c r="L9" s="36"/>
       <c r="M9" s="37"/>
@@ -8760,41 +8792,41 @@
     </row>
     <row r="10" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="28" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C10" s="30">
         <v>30</v>
       </c>
       <c r="D10" s="30">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E10" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F10" s="32">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G10" s="30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H10" s="33">
         <v>0</v>
       </c>
       <c r="I10" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="J10" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.48333333333333334</v>
       </c>
       <c r="K10" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="L10" s="36"/>
       <c r="M10" s="37"/>
@@ -8813,41 +8845,41 @@
     </row>
     <row r="11" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C11" s="30">
         <v>30</v>
       </c>
       <c r="D11" s="30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E11" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F11" s="32">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G11" s="30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H11" s="33">
         <v>0</v>
       </c>
       <c r="I11" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="J11" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.49166666666666664</v>
       </c>
       <c r="K11" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.51583333333333337</v>
       </c>
       <c r="L11" s="36"/>
       <c r="M11" s="37"/>
@@ -8866,41 +8898,41 @@
     </row>
     <row r="12" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C12" s="30">
         <v>30</v>
       </c>
       <c r="D12" s="30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E12" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="F12" s="32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G12" s="30">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H12" s="33">
         <v>0</v>
       </c>
       <c r="I12" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J12" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="K12" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="L12" s="36"/>
       <c r="M12" s="37"/>
@@ -8919,41 +8951,41 @@
     </row>
     <row r="13" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="28" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C13" s="30">
         <v>30</v>
       </c>
       <c r="D13" s="30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E13" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F13" s="32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G13" s="30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H13" s="33">
         <v>0</v>
       </c>
       <c r="I13" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J13" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="K13" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.41083333333333338</v>
       </c>
       <c r="L13" s="36"/>
       <c r="M13" s="37"/>
@@ -8972,41 +9004,41 @@
     </row>
     <row r="14" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="28" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="30">
         <v>30</v>
       </c>
       <c r="D14" s="30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E14" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="F14" s="32">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G14" s="30">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H14" s="33">
         <v>0</v>
       </c>
       <c r="I14" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J14" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.25833333333333336</v>
       </c>
       <c r="K14" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.27916666666666673</v>
       </c>
       <c r="L14" s="36"/>
       <c r="M14" s="37"/>
@@ -9025,41 +9057,41 @@
     </row>
     <row r="15" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="28" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" s="30">
         <v>30</v>
       </c>
       <c r="D15" s="30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E15" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="F15" s="32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G15" s="30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H15" s="33">
         <v>0</v>
       </c>
       <c r="I15" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J15" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="K15" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.42416666666666669</v>
       </c>
       <c r="L15" s="36"/>
       <c r="M15" s="37"/>
@@ -9078,41 +9110,41 @@
     </row>
     <row r="16" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="28" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C16" s="30">
         <v>30</v>
       </c>
       <c r="D16" s="30">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E16" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.73333333333333328</v>
       </c>
       <c r="F16" s="32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G16" s="30">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H16" s="33">
         <v>0</v>
       </c>
       <c r="I16" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J16" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="K16" s="35">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.36583333333333334</v>
       </c>
       <c r="L16" s="36"/>
       <c r="M16" s="37"/>
@@ -9131,41 +9163,41 @@
     </row>
     <row r="17" spans="1:25" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C17" s="30">
         <v>30</v>
       </c>
       <c r="D17" s="30">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E17" s="31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="F17" s="32">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G17" s="30">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H17" s="33">
         <v>0</v>
       </c>
       <c r="I17" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J17" s="34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.40833333333333333</v>
       </c>
       <c r="K17" s="35">
         <f t="shared" ref="K17" si="4">E17*0.1+J17*0.9</f>
-        <v>0</v>
+        <v>0.46083333333333332</v>
       </c>
       <c r="L17" s="36"/>
       <c r="M17" s="37"/>
@@ -9246,7 +9278,7 @@
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
       <c r="E20" s="40" t="s">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="F20" s="38">
         <v>2</v>
@@ -9277,7 +9309,7 @@
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
       <c r="E21" s="40" t="s">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="F21" s="38">
         <v>3</v>
@@ -9308,7 +9340,7 @@
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
       <c r="E22" s="40" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="F22" s="38">
         <v>4</v>
@@ -9339,7 +9371,7 @@
       <c r="C23" s="37"/>
       <c r="D23" s="37"/>
       <c r="E23" s="40" t="s">
-        <v>34</v>
+        <v>146</v>
       </c>
       <c r="F23" s="38">
         <v>5</v>
